--- a/docs/컬렉션.xlsx
+++ b/docs/컬렉션.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'컬렉션'!$A$1:$U$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'컬렉션'!$A$1:$T$118</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U118"/>
+  <dimension ref="A1:T118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -670,11 +670,6 @@
           <t>도시 키</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>등급 지정</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -718,11 +713,11 @@
         <v/>
       </c>
       <c r="J2" s="2">
-        <f>IF(U2&lt;&gt;"",U2,INDEX(비용표!$A$13:$A$17,MATCH(I2,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I2,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K2" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J2,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I2,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -756,7 +751,6 @@
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -800,11 +794,11 @@
         <v/>
       </c>
       <c r="J3" s="2">
-        <f>IF(U3&lt;&gt;"",U3,INDEX(비용표!$A$13:$A$17,MATCH(I3,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I3,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K3" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J3,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I3,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -830,7 +824,6 @@
           <t>raidLoot</t>
         </is>
       </c>
-      <c r="U3" s="2" t="n"/>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -874,11 +867,11 @@
         <v/>
       </c>
       <c r="J4" s="2">
-        <f>IF(U4&lt;&gt;"",U4,INDEX(비용표!$A$13:$A$17,MATCH(I4,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I4,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K4" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J4,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I4,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -912,7 +905,6 @@
         </is>
       </c>
       <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -956,11 +948,11 @@
         <v/>
       </c>
       <c r="J5" s="2">
-        <f>IF(U5&lt;&gt;"",U5,INDEX(비용표!$A$13:$A$17,MATCH(I5,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I5,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K5" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J5,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I5,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -994,7 +986,6 @@
         </is>
       </c>
       <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -1038,11 +1029,11 @@
         <v/>
       </c>
       <c r="J6" s="2">
-        <f>IF(U6&lt;&gt;"",U6,INDEX(비용표!$A$13:$A$17,MATCH(I6,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I6,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K6" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J6,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I6,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1072,7 +1063,6 @@
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1116,11 +1106,11 @@
         <v/>
       </c>
       <c r="J7" s="2">
-        <f>IF(U7&lt;&gt;"",U7,INDEX(비용표!$A$13:$A$17,MATCH(I7,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I7,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K7" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J7,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I7,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1150,7 +1140,6 @@
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="2" t="n"/>
-      <c r="U7" s="2" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1194,11 +1183,11 @@
         <v/>
       </c>
       <c r="J8" s="2">
-        <f>IF(U8&lt;&gt;"",U8,INDEX(비용표!$A$13:$A$17,MATCH(I8,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I8,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K8" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J8,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I8,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1232,7 +1221,6 @@
         </is>
       </c>
       <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -1276,11 +1264,11 @@
         <v/>
       </c>
       <c r="J9" s="2">
-        <f>IF(U9&lt;&gt;"",U9,INDEX(비용표!$A$13:$A$17,MATCH(I9,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I9,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K9" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J9,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I9,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1314,7 +1302,6 @@
         </is>
       </c>
       <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -1358,11 +1345,11 @@
         <v/>
       </c>
       <c r="J10" s="2">
-        <f>IF(U10&lt;&gt;"",U10,INDEX(비용표!$A$13:$A$17,MATCH(I10,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I10,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K10" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J10,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I10,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1396,7 +1383,6 @@
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1440,11 +1426,11 @@
         <v/>
       </c>
       <c r="J11" s="2">
-        <f>IF(U11&lt;&gt;"",U11,INDEX(비용표!$A$13:$A$17,MATCH(I11,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I11,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K11" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J11,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I11,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1474,7 +1460,6 @@
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1518,11 +1503,11 @@
         <v/>
       </c>
       <c r="J12" s="2">
-        <f>IF(U12&lt;&gt;"",U12,INDEX(비용표!$A$13:$A$17,MATCH(I12,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I12,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K12" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J12,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I12,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1556,7 +1541,6 @@
         </is>
       </c>
       <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -1600,11 +1584,11 @@
         <v/>
       </c>
       <c r="J13" s="2">
-        <f>IF(U13&lt;&gt;"",U13,INDEX(비용표!$A$13:$A$17,MATCH(I13,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I13,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K13" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J13,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I13,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1634,7 +1618,6 @@
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="2" t="n"/>
-      <c r="U13" s="2" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1678,11 +1661,11 @@
         <v/>
       </c>
       <c r="J14" s="2">
-        <f>IF(U14&lt;&gt;"",U14,INDEX(비용표!$A$13:$A$17,MATCH(I14,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I14,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K14" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J14,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I14,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1716,7 +1699,6 @@
         </is>
       </c>
       <c r="T14" s="2" t="n"/>
-      <c r="U14" s="2" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -1760,11 +1742,11 @@
         <v/>
       </c>
       <c r="J15" s="2">
-        <f>IF(U15&lt;&gt;"",U15,INDEX(비용표!$A$13:$A$17,MATCH(I15,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I15,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K15" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J15,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I15,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1798,7 +1780,6 @@
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n"/>
-      <c r="U15" s="2" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1842,11 +1823,11 @@
         <v/>
       </c>
       <c r="J16" s="2">
-        <f>IF(U16&lt;&gt;"",U16,INDEX(비용표!$A$13:$A$17,MATCH(I16,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I16,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K16" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J16,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I16,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1872,7 +1853,6 @@
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1916,11 +1896,11 @@
         <v/>
       </c>
       <c r="J17" s="2">
-        <f>IF(U17&lt;&gt;"",U17,INDEX(비용표!$A$13:$A$17,MATCH(I17,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I17,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K17" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J17,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I17,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1946,7 +1926,6 @@
           <t>grainRate</t>
         </is>
       </c>
-      <c r="U17" s="2" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -1990,11 +1969,11 @@
         <v/>
       </c>
       <c r="J18" s="2">
-        <f>IF(U18&lt;&gt;"",U18,INDEX(비용표!$A$13:$A$17,MATCH(I18,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I18,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K18" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J18,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I18,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -2024,7 +2003,6 @@
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="n"/>
-      <c r="U18" s="2" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -2068,11 +2046,11 @@
         <v/>
       </c>
       <c r="J19" s="2">
-        <f>IF(U19&lt;&gt;"",U19,INDEX(비용표!$A$13:$A$17,MATCH(I19,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I19,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K19" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J19,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I19,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2106,7 +2084,6 @@
         </is>
       </c>
       <c r="T19" s="2" t="n"/>
-      <c r="U19" s="2" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -2150,11 +2127,11 @@
         <v/>
       </c>
       <c r="J20" s="2">
-        <f>IF(U20&lt;&gt;"",U20,INDEX(비용표!$A$13:$A$17,MATCH(I20,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I20,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K20" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J20,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I20,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -2184,7 +2161,6 @@
       <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="n"/>
-      <c r="U20" s="2" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -2228,11 +2204,11 @@
         <v/>
       </c>
       <c r="J21" s="2">
-        <f>IF(U21&lt;&gt;"",U21,INDEX(비용표!$A$13:$A$17,MATCH(I21,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I21,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K21" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J21,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I21,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2266,7 +2242,6 @@
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="n"/>
-      <c r="U21" s="2" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -2310,11 +2285,11 @@
         <v/>
       </c>
       <c r="J22" s="2">
-        <f>IF(U22&lt;&gt;"",U22,INDEX(비용표!$A$13:$A$17,MATCH(I22,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I22,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K22" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J22,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I22,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -2340,11 +2315,6 @@
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="2" t="n"/>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -2388,11 +2358,11 @@
         <v/>
       </c>
       <c r="J23" s="2">
-        <f>IF(U23&lt;&gt;"",U23,INDEX(비용표!$A$13:$A$17,MATCH(I23,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I23,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K23" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J23,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I23,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2422,7 +2392,6 @@
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="2" t="n"/>
-      <c r="U23" s="2" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -2466,11 +2435,11 @@
         <v/>
       </c>
       <c r="J24" s="2">
-        <f>IF(U24&lt;&gt;"",U24,INDEX(비용표!$A$13:$A$17,MATCH(I24,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I24,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K24" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J24,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I24,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2504,7 +2473,6 @@
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="2" t="n"/>
-      <c r="U24" s="2" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -2548,11 +2516,11 @@
         <v/>
       </c>
       <c r="J25" s="2">
-        <f>IF(U25&lt;&gt;"",U25,INDEX(비용표!$A$13:$A$17,MATCH(I25,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I25,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K25" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J25,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I25,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2582,7 +2550,6 @@
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="n"/>
-      <c r="U25" s="2" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -2626,11 +2593,11 @@
         <v/>
       </c>
       <c r="J26" s="2">
-        <f>IF(U26&lt;&gt;"",U26,INDEX(비용표!$A$13:$A$17,MATCH(I26,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I26,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K26" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J26,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I26,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2656,7 +2623,6 @@
           <t>grainCap</t>
         </is>
       </c>
-      <c r="U26" s="2" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="n">
@@ -2700,11 +2666,11 @@
         <v/>
       </c>
       <c r="J27" s="2">
-        <f>IF(U27&lt;&gt;"",U27,INDEX(비용표!$A$13:$A$17,MATCH(I27,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I27,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K27" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J27,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I27,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2734,7 +2700,6 @@
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="2" t="n"/>
-      <c r="U27" s="2" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -2778,11 +2743,11 @@
         <v/>
       </c>
       <c r="J28" s="2">
-        <f>IF(U28&lt;&gt;"",U28,INDEX(비용표!$A$13:$A$17,MATCH(I28,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I28,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K28" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J28,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I28,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2812,7 +2777,6 @@
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="n"/>
-      <c r="U28" s="2" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="2" t="n">
@@ -2856,11 +2820,11 @@
         <v/>
       </c>
       <c r="J29" s="2">
-        <f>IF(U29&lt;&gt;"",U29,INDEX(비용표!$A$13:$A$17,MATCH(I29,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I29,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K29" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J29,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I29,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2890,7 +2854,6 @@
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="2" t="n"/>
-      <c r="U29" s="2" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -2934,11 +2897,11 @@
         <v/>
       </c>
       <c r="J30" s="2">
-        <f>IF(U30&lt;&gt;"",U30,INDEX(비용표!$A$13:$A$17,MATCH(I30,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I30,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K30" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J30,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I30,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2968,7 +2931,6 @@
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="n"/>
-      <c r="U30" s="2" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -3012,11 +2974,11 @@
         <v/>
       </c>
       <c r="J31" s="2">
-        <f>IF(U31&lt;&gt;"",U31,INDEX(비용표!$A$13:$A$17,MATCH(I31,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I31,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K31" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J31,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I31,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3046,7 +3008,6 @@
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="2" t="n"/>
-      <c r="U31" s="2" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -3090,11 +3051,11 @@
         <v/>
       </c>
       <c r="J32" s="2">
-        <f>IF(U32&lt;&gt;"",U32,INDEX(비용표!$A$13:$A$17,MATCH(I32,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I32,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K32" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J32,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I32,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -3128,7 +3089,6 @@
         </is>
       </c>
       <c r="T32" s="2" t="n"/>
-      <c r="U32" s="2" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -3172,11 +3132,11 @@
         <v/>
       </c>
       <c r="J33" s="2">
-        <f>IF(U33&lt;&gt;"",U33,INDEX(비용표!$A$13:$A$17,MATCH(I33,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I33,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K33" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J33,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I33,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3210,7 +3170,6 @@
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="n"/>
-      <c r="U33" s="2" t="n"/>
     </row>
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -3254,11 +3213,11 @@
         <v/>
       </c>
       <c r="J34" s="2">
-        <f>IF(U34&lt;&gt;"",U34,INDEX(비용표!$A$13:$A$17,MATCH(I34,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I34,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K34" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J34,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I34,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -3288,7 +3247,6 @@
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -3332,11 +3290,11 @@
         <v/>
       </c>
       <c r="J35" s="2">
-        <f>IF(U35&lt;&gt;"",U35,INDEX(비용표!$A$13:$A$17,MATCH(I35,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I35,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K35" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J35,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I35,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3366,7 +3324,6 @@
       <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="n"/>
-      <c r="U35" s="2" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -3410,11 +3367,11 @@
         <v/>
       </c>
       <c r="J36" s="2">
-        <f>IF(U36&lt;&gt;"",U36,INDEX(비용표!$A$13:$A$17,MATCH(I36,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I36,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K36" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J36,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I36,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -3448,7 +3405,6 @@
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="n"/>
-      <c r="U36" s="2" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="2" t="n">
@@ -3492,11 +3448,11 @@
         <v/>
       </c>
       <c r="J37" s="2">
-        <f>IF(U37&lt;&gt;"",U37,INDEX(비용표!$A$13:$A$17,MATCH(I37,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I37,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K37" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J37,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I37,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3530,7 +3486,6 @@
       <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="n"/>
-      <c r="U37" s="2" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -3574,11 +3529,11 @@
         <v/>
       </c>
       <c r="J38" s="2">
-        <f>IF(U38&lt;&gt;"",U38,INDEX(비용표!$A$13:$A$17,MATCH(I38,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I38,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K38" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J38,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I38,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -3612,7 +3567,6 @@
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="n"/>
-      <c r="U38" s="2" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="2" t="n">
@@ -3656,11 +3610,11 @@
         <v/>
       </c>
       <c r="J39" s="2">
-        <f>IF(U39&lt;&gt;"",U39,INDEX(비용표!$A$13:$A$17,MATCH(I39,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I39,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K39" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J39,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I39,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3698,11 +3652,6 @@
         </is>
       </c>
       <c r="T39" s="2" t="n"/>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>천하</t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -3746,11 +3695,11 @@
         <v/>
       </c>
       <c r="J40" s="2">
-        <f>IF(U40&lt;&gt;"",U40,INDEX(비용표!$A$13:$A$17,MATCH(I40,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I40,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K40" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J40,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I40,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -3776,7 +3725,6 @@
           <t>grainCap</t>
         </is>
       </c>
-      <c r="U40" s="2" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="2" t="n">
@@ -3820,11 +3768,11 @@
         <v/>
       </c>
       <c r="J41" s="2">
-        <f>IF(U41&lt;&gt;"",U41,INDEX(비용표!$A$13:$A$17,MATCH(I41,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I41,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K41" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J41,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I41,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3854,7 +3802,6 @@
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="n"/>
-      <c r="U41" s="2" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -3898,11 +3845,11 @@
         <v/>
       </c>
       <c r="J42" s="2">
-        <f>IF(U42&lt;&gt;"",U42,INDEX(비용표!$A$13:$A$17,MATCH(I42,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I42,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K42" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J42,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I42,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -3936,7 +3883,6 @@
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="n"/>
-      <c r="U42" s="2" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="2" t="n">
@@ -3980,11 +3926,11 @@
         <v/>
       </c>
       <c r="J43" s="2">
-        <f>IF(U43&lt;&gt;"",U43,INDEX(비용표!$A$13:$A$17,MATCH(I43,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I43,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K43" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J43,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I43,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4014,7 +3960,6 @@
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="n"/>
-      <c r="U43" s="2" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -4058,11 +4003,11 @@
         <v/>
       </c>
       <c r="J44" s="2">
-        <f>IF(U44&lt;&gt;"",U44,INDEX(비용표!$A$13:$A$17,MATCH(I44,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I44,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K44" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J44,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I44,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -4092,7 +4037,6 @@
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="n"/>
-      <c r="U44" s="2" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="2" t="n">
@@ -4136,11 +4080,11 @@
         <v/>
       </c>
       <c r="J45" s="2">
-        <f>IF(U45&lt;&gt;"",U45,INDEX(비용표!$A$13:$A$17,MATCH(I45,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I45,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K45" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J45,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I45,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4170,7 +4114,6 @@
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="n"/>
-      <c r="U45" s="2" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -4214,11 +4157,11 @@
         <v/>
       </c>
       <c r="J46" s="2">
-        <f>IF(U46&lt;&gt;"",U46,INDEX(비용표!$A$13:$A$17,MATCH(I46,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I46,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K46" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J46,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I46,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -4252,7 +4195,6 @@
         </is>
       </c>
       <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="2" t="n">
@@ -4296,11 +4238,11 @@
         <v/>
       </c>
       <c r="J47" s="2">
-        <f>IF(U47&lt;&gt;"",U47,INDEX(비용표!$A$13:$A$17,MATCH(I47,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I47,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K47" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J47,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I47,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4330,7 +4272,6 @@
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="2" t="n"/>
-      <c r="U47" s="2" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -4374,11 +4315,11 @@
         <v/>
       </c>
       <c r="J48" s="2">
-        <f>IF(U48&lt;&gt;"",U48,INDEX(비용표!$A$13:$A$17,MATCH(I48,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I48,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K48" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J48,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I48,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -4404,7 +4345,6 @@
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="n"/>
-      <c r="U48" s="2" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="2" t="n">
@@ -4448,11 +4388,11 @@
         <v/>
       </c>
       <c r="J49" s="2">
-        <f>IF(U49&lt;&gt;"",U49,INDEX(비용표!$A$13:$A$17,MATCH(I49,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I49,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K49" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J49,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I49,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4482,7 +4422,6 @@
       <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="2" t="n"/>
-      <c r="U49" s="2" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -4526,11 +4465,11 @@
         <v/>
       </c>
       <c r="J50" s="2">
-        <f>IF(U50&lt;&gt;"",U50,INDEX(비용표!$A$13:$A$17,MATCH(I50,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I50,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K50" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J50,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I50,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -4560,7 +4499,6 @@
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="2" t="n"/>
-      <c r="U50" s="2" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="2" t="n">
@@ -4604,11 +4542,11 @@
         <v/>
       </c>
       <c r="J51" s="2">
-        <f>IF(U51&lt;&gt;"",U51,INDEX(비용표!$A$13:$A$17,MATCH(I51,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I51,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K51" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J51,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I51,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4638,7 +4576,6 @@
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="2" t="n"/>
-      <c r="U51" s="2" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -4682,11 +4619,11 @@
         <v/>
       </c>
       <c r="J52" s="2">
-        <f>IF(U52&lt;&gt;"",U52,INDEX(비용표!$A$13:$A$17,MATCH(I52,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I52,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K52" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J52,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I52,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -4712,7 +4649,6 @@
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="n"/>
-      <c r="U52" s="2" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="2" t="n">
@@ -4756,11 +4692,11 @@
         <v/>
       </c>
       <c r="J53" s="2">
-        <f>IF(U53&lt;&gt;"",U53,INDEX(비용표!$A$13:$A$17,MATCH(I53,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I53,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K53" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J53,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I53,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4790,7 +4726,6 @@
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="2" t="n"/>
-      <c r="U53" s="2" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -4834,11 +4769,11 @@
         <v/>
       </c>
       <c r="J54" s="2">
-        <f>IF(U54&lt;&gt;"",U54,INDEX(비용표!$A$13:$A$17,MATCH(I54,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I54,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K54" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J54,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I54,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -4868,7 +4803,6 @@
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="n"/>
-      <c r="U54" s="2" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="2" t="n">
@@ -4912,11 +4846,11 @@
         <v/>
       </c>
       <c r="J55" s="2">
-        <f>IF(U55&lt;&gt;"",U55,INDEX(비용표!$A$13:$A$17,MATCH(I55,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I55,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K55" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J55,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I55,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -4942,11 +4876,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>영웅</t>
-        </is>
-      </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -4990,11 +4919,11 @@
         <v/>
       </c>
       <c r="J56" s="2">
-        <f>IF(U56&lt;&gt;"",U56,INDEX(비용표!$A$13:$A$17,MATCH(I56,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I56,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K56" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J56,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I56,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -5024,7 +4953,6 @@
       <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="2" t="n"/>
-      <c r="U56" s="2" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="2" t="n">
@@ -5068,11 +4996,11 @@
         <v/>
       </c>
       <c r="J57" s="2">
-        <f>IF(U57&lt;&gt;"",U57,INDEX(비용표!$A$13:$A$17,MATCH(I57,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I57,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K57" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J57,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I57,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5102,7 +5030,6 @@
       <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="2" t="n"/>
-      <c r="U57" s="2" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -5146,11 +5073,11 @@
         <v/>
       </c>
       <c r="J58" s="2">
-        <f>IF(U58&lt;&gt;"",U58,INDEX(비용표!$A$13:$A$17,MATCH(I58,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I58,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K58" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J58,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I58,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -5176,7 +5103,6 @@
           <t>forge</t>
         </is>
       </c>
-      <c r="U58" s="2" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="2" t="n">
@@ -5220,11 +5146,11 @@
         <v/>
       </c>
       <c r="J59" s="2">
-        <f>IF(U59&lt;&gt;"",U59,INDEX(비용표!$A$13:$A$17,MATCH(I59,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I59,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K59" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J59,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I59,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5258,7 +5184,6 @@
       <c r="R59" s="2" t="n"/>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="2" t="n"/>
-      <c r="U59" s="2" t="n"/>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -5302,11 +5227,11 @@
         <v/>
       </c>
       <c r="J60" s="2">
-        <f>IF(U60&lt;&gt;"",U60,INDEX(비용표!$A$13:$A$17,MATCH(I60,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I60,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K60" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J60,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I60,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -5336,7 +5261,6 @@
       <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="2" t="n"/>
-      <c r="U60" s="2" t="n"/>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="2" t="n">
@@ -5380,11 +5304,11 @@
         <v/>
       </c>
       <c r="J61" s="2">
-        <f>IF(U61&lt;&gt;"",U61,INDEX(비용표!$A$13:$A$17,MATCH(I61,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I61,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K61" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J61,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I61,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -5410,7 +5334,6 @@
       <c r="R61" s="2" t="n"/>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="2" t="n"/>
-      <c r="U61" s="2" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -5454,11 +5377,11 @@
         <v/>
       </c>
       <c r="J62" s="2">
-        <f>IF(U62&lt;&gt;"",U62,INDEX(비용표!$A$13:$A$17,MATCH(I62,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I62,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K62" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J62,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I62,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -5484,11 +5407,6 @@
       <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="2" t="n"/>
-      <c r="U62" s="2" t="inlineStr">
-        <is>
-          <t>천하</t>
-        </is>
-      </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="2" t="n">
@@ -5532,11 +5450,11 @@
         <v/>
       </c>
       <c r="J63" s="2">
-        <f>IF(U63&lt;&gt;"",U63,INDEX(비용표!$A$13:$A$17,MATCH(I63,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I63,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K63" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J63,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I63,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -5570,7 +5488,6 @@
         </is>
       </c>
       <c r="T63" s="2" t="n"/>
-      <c r="U63" s="2" t="n"/>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -5614,11 +5531,11 @@
         <v/>
       </c>
       <c r="J64" s="2">
-        <f>IF(U64&lt;&gt;"",U64,INDEX(비용표!$A$13:$A$17,MATCH(I64,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I64,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K64" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J64,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I64,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -5648,7 +5565,6 @@
       <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="n"/>
-      <c r="U64" s="2" t="n"/>
     </row>
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="2" t="n">
@@ -5692,11 +5608,11 @@
         <v/>
       </c>
       <c r="J65" s="2">
-        <f>IF(U65&lt;&gt;"",U65,INDEX(비용표!$A$13:$A$17,MATCH(I65,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I65,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K65" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J65,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I65,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -5730,7 +5646,6 @@
         </is>
       </c>
       <c r="T65" s="2" t="n"/>
-      <c r="U65" s="2" t="n"/>
     </row>
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="2" t="n">
@@ -5774,11 +5689,11 @@
         <v/>
       </c>
       <c r="J66" s="2">
-        <f>IF(U66&lt;&gt;"",U66,INDEX(비용표!$A$13:$A$17,MATCH(I66,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I66,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K66" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J66,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I66,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -5812,7 +5727,6 @@
         </is>
       </c>
       <c r="T66" s="2" t="n"/>
-      <c r="U66" s="2" t="n"/>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="2" t="n">
@@ -5856,11 +5770,11 @@
         <v/>
       </c>
       <c r="J67" s="2">
-        <f>IF(U67&lt;&gt;"",U67,INDEX(비용표!$A$13:$A$17,MATCH(I67,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I67,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K67" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J67,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I67,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -5894,7 +5808,6 @@
       <c r="R67" s="2" t="n"/>
       <c r="S67" s="2" t="n"/>
       <c r="T67" s="2" t="n"/>
-      <c r="U67" s="2" t="n"/>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -5938,11 +5851,11 @@
         <v/>
       </c>
       <c r="J68" s="2">
-        <f>IF(U68&lt;&gt;"",U68,INDEX(비용표!$A$13:$A$17,MATCH(I68,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I68,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K68" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J68,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I68,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -5972,7 +5885,6 @@
       <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="2" t="n"/>
-      <c r="U68" s="2" t="n"/>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="2" t="n">
@@ -6016,11 +5928,11 @@
         <v/>
       </c>
       <c r="J69" s="2">
-        <f>IF(U69&lt;&gt;"",U69,INDEX(비용표!$A$13:$A$17,MATCH(I69,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I69,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K69" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J69,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I69,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6054,7 +5966,6 @@
       <c r="R69" s="2" t="n"/>
       <c r="S69" s="2" t="n"/>
       <c r="T69" s="2" t="n"/>
-      <c r="U69" s="2" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="2" t="n">
@@ -6098,11 +6009,11 @@
         <v/>
       </c>
       <c r="J70" s="2">
-        <f>IF(U70&lt;&gt;"",U70,INDEX(비용표!$A$13:$A$17,MATCH(I70,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I70,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K70" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J70,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I70,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -6128,7 +6039,6 @@
           <t>raidResp</t>
         </is>
       </c>
-      <c r="U70" s="2" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="2" t="n">
@@ -6172,11 +6082,11 @@
         <v/>
       </c>
       <c r="J71" s="2">
-        <f>IF(U71&lt;&gt;"",U71,INDEX(비용표!$A$13:$A$17,MATCH(I71,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I71,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K71" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J71,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I71,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6210,7 +6120,6 @@
         </is>
       </c>
       <c r="T71" s="2" t="n"/>
-      <c r="U71" s="2" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="2" t="n">
@@ -6254,11 +6163,11 @@
         <v/>
       </c>
       <c r="J72" s="2">
-        <f>IF(U72&lt;&gt;"",U72,INDEX(비용표!$A$13:$A$17,MATCH(I72,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I72,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K72" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J72,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I72,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -6292,7 +6201,6 @@
       <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="n"/>
-      <c r="U72" s="2" t="n"/>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="2" t="n">
@@ -6336,11 +6244,11 @@
         <v/>
       </c>
       <c r="J73" s="2">
-        <f>IF(U73&lt;&gt;"",U73,INDEX(비용표!$A$13:$A$17,MATCH(I73,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I73,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K73" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J73,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I73,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6374,7 +6282,6 @@
         </is>
       </c>
       <c r="T73" s="2" t="n"/>
-      <c r="U73" s="2" t="n"/>
     </row>
     <row r="74" ht="32" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -6418,11 +6325,11 @@
         <v/>
       </c>
       <c r="J74" s="2">
-        <f>IF(U74&lt;&gt;"",U74,INDEX(비용표!$A$13:$A$17,MATCH(I74,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I74,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K74" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J74,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I74,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -6452,7 +6359,6 @@
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="n"/>
-      <c r="U74" s="2" t="n"/>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="2" t="n">
@@ -6496,11 +6402,11 @@
         <v/>
       </c>
       <c r="J75" s="2">
-        <f>IF(U75&lt;&gt;"",U75,INDEX(비용표!$A$13:$A$17,MATCH(I75,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I75,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K75" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J75,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I75,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -6534,7 +6440,6 @@
         </is>
       </c>
       <c r="T75" s="2" t="n"/>
-      <c r="U75" s="2" t="n"/>
     </row>
     <row r="76" ht="32" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -6578,11 +6483,11 @@
         <v/>
       </c>
       <c r="J76" s="2">
-        <f>IF(U76&lt;&gt;"",U76,INDEX(비용표!$A$13:$A$17,MATCH(I76,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I76,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K76" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J76,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I76,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -6612,7 +6517,6 @@
       <c r="R76" s="2" t="n"/>
       <c r="S76" s="2" t="n"/>
       <c r="T76" s="2" t="n"/>
-      <c r="U76" s="2" t="n"/>
     </row>
     <row r="77" ht="32" customHeight="1">
       <c r="A77" s="2" t="n">
@@ -6656,11 +6560,11 @@
         <v/>
       </c>
       <c r="J77" s="2">
-        <f>IF(U77&lt;&gt;"",U77,INDEX(비용표!$A$13:$A$17,MATCH(I77,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I77,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K77" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J77,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I77,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -6690,7 +6594,6 @@
       <c r="R77" s="2" t="n"/>
       <c r="S77" s="2" t="n"/>
       <c r="T77" s="2" t="n"/>
-      <c r="U77" s="2" t="n"/>
     </row>
     <row r="78" ht="32" customHeight="1">
       <c r="A78" s="2" t="n">
@@ -6734,11 +6637,11 @@
         <v/>
       </c>
       <c r="J78" s="2">
-        <f>IF(U78&lt;&gt;"",U78,INDEX(비용표!$A$13:$A$17,MATCH(I78,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I78,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K78" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J78,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I78,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -6768,7 +6671,6 @@
       <c r="R78" s="2" t="n"/>
       <c r="S78" s="2" t="n"/>
       <c r="T78" s="2" t="n"/>
-      <c r="U78" s="2" t="n"/>
     </row>
     <row r="79" ht="32" customHeight="1">
       <c r="A79" s="2" t="n">
@@ -6812,11 +6714,11 @@
         <v/>
       </c>
       <c r="J79" s="2">
-        <f>IF(U79&lt;&gt;"",U79,INDEX(비용표!$A$13:$A$17,MATCH(I79,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I79,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K79" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J79,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I79,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -6842,11 +6744,6 @@
       <c r="R79" s="2" t="n"/>
       <c r="S79" s="2" t="n"/>
       <c r="T79" s="2" t="n"/>
-      <c r="U79" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="80" ht="32" customHeight="1">
       <c r="A80" s="2" t="n">
@@ -6890,11 +6787,11 @@
         <v/>
       </c>
       <c r="J80" s="2">
-        <f>IF(U80&lt;&gt;"",U80,INDEX(비용표!$A$13:$A$17,MATCH(I80,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I80,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K80" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J80,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I80,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -6924,7 +6821,6 @@
       <c r="R80" s="2" t="n"/>
       <c r="S80" s="2" t="n"/>
       <c r="T80" s="2" t="n"/>
-      <c r="U80" s="2" t="n"/>
     </row>
     <row r="81" ht="32" customHeight="1">
       <c r="A81" s="2" t="n">
@@ -6968,11 +6864,11 @@
         <v/>
       </c>
       <c r="J81" s="2">
-        <f>IF(U81&lt;&gt;"",U81,INDEX(비용표!$A$13:$A$17,MATCH(I81,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I81,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K81" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J81,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I81,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -6998,11 +6894,6 @@
       <c r="R81" s="2" t="n"/>
       <c r="S81" s="2" t="n"/>
       <c r="T81" s="2" t="n"/>
-      <c r="U81" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -7046,11 +6937,11 @@
         <v/>
       </c>
       <c r="J82" s="2">
-        <f>IF(U82&lt;&gt;"",U82,INDEX(비용표!$A$13:$A$17,MATCH(I82,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I82,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K82" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J82,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I82,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -7080,7 +6971,6 @@
       <c r="R82" s="2" t="n"/>
       <c r="S82" s="2" t="n"/>
       <c r="T82" s="2" t="n"/>
-      <c r="U82" s="2" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="2" t="n">
@@ -7124,11 +7014,11 @@
         <v/>
       </c>
       <c r="J83" s="2">
-        <f>IF(U83&lt;&gt;"",U83,INDEX(비용표!$A$13:$A$17,MATCH(I83,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I83,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K83" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J83,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I83,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7158,7 +7048,6 @@
       <c r="R83" s="2" t="n"/>
       <c r="S83" s="2" t="n"/>
       <c r="T83" s="2" t="n"/>
-      <c r="U83" s="2" t="n"/>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="2" t="n">
@@ -7202,11 +7091,11 @@
         <v/>
       </c>
       <c r="J84" s="2">
-        <f>IF(U84&lt;&gt;"",U84,INDEX(비용표!$A$13:$A$17,MATCH(I84,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I84,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K84" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J84,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I84,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -7240,7 +7129,6 @@
         </is>
       </c>
       <c r="T84" s="2" t="n"/>
-      <c r="U84" s="2" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="2" t="n">
@@ -7284,11 +7172,11 @@
         <v/>
       </c>
       <c r="J85" s="2">
-        <f>IF(U85&lt;&gt;"",U85,INDEX(비용표!$A$13:$A$17,MATCH(I85,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I85,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K85" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J85,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I85,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -7314,7 +7202,6 @@
       <c r="R85" s="2" t="n"/>
       <c r="S85" s="2" t="n"/>
       <c r="T85" s="2" t="n"/>
-      <c r="U85" s="2" t="n"/>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="2" t="n">
@@ -7358,11 +7245,11 @@
         <v/>
       </c>
       <c r="J86" s="2">
-        <f>IF(U86&lt;&gt;"",U86,INDEX(비용표!$A$13:$A$17,MATCH(I86,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I86,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K86" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J86,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I86,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -7396,7 +7283,6 @@
       <c r="R86" s="2" t="n"/>
       <c r="S86" s="2" t="n"/>
       <c r="T86" s="2" t="n"/>
-      <c r="U86" s="2" t="n"/>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="2" t="n">
@@ -7440,11 +7326,11 @@
         <v/>
       </c>
       <c r="J87" s="2">
-        <f>IF(U87&lt;&gt;"",U87,INDEX(비용표!$A$13:$A$17,MATCH(I87,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I87,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K87" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J87,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I87,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -7474,7 +7360,6 @@
       <c r="R87" s="2" t="n"/>
       <c r="S87" s="2" t="n"/>
       <c r="T87" s="2" t="n"/>
-      <c r="U87" s="2" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -7518,11 +7403,11 @@
         <v/>
       </c>
       <c r="J88" s="2">
-        <f>IF(U88&lt;&gt;"",U88,INDEX(비용표!$A$13:$A$17,MATCH(I88,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I88,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K88" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J88,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I88,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -7556,7 +7441,6 @@
         </is>
       </c>
       <c r="T88" s="2" t="n"/>
-      <c r="U88" s="2" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="2" t="n">
@@ -7600,11 +7484,11 @@
         <v/>
       </c>
       <c r="J89" s="2">
-        <f>IF(U89&lt;&gt;"",U89,INDEX(비용표!$A$13:$A$17,MATCH(I89,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I89,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K89" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J89,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I89,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -7638,7 +7522,6 @@
       <c r="R89" s="2" t="n"/>
       <c r="S89" s="2" t="n"/>
       <c r="T89" s="2" t="n"/>
-      <c r="U89" s="2" t="n"/>
     </row>
     <row r="90" ht="32" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -7682,11 +7565,11 @@
         <v/>
       </c>
       <c r="J90" s="2">
-        <f>IF(U90&lt;&gt;"",U90,INDEX(비용표!$A$13:$A$17,MATCH(I90,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I90,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K90" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J90,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I90,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -7720,7 +7603,6 @@
         </is>
       </c>
       <c r="T90" s="2" t="n"/>
-      <c r="U90" s="2" t="n"/>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -7764,11 +7646,11 @@
         <v/>
       </c>
       <c r="J91" s="2">
-        <f>IF(U91&lt;&gt;"",U91,INDEX(비용표!$A$13:$A$17,MATCH(I91,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I91,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K91" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J91,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I91,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -7794,11 +7676,6 @@
       <c r="R91" s="2" t="n"/>
       <c r="S91" s="2" t="n"/>
       <c r="T91" s="2" t="n"/>
-      <c r="U91" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="92" ht="32" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -7842,11 +7719,11 @@
         <v/>
       </c>
       <c r="J92" s="2">
-        <f>IF(U92&lt;&gt;"",U92,INDEX(비용표!$A$13:$A$17,MATCH(I92,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I92,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K92" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J92,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I92,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -7880,7 +7757,6 @@
       <c r="R92" s="2" t="n"/>
       <c r="S92" s="2" t="n"/>
       <c r="T92" s="2" t="n"/>
-      <c r="U92" s="2" t="n"/>
     </row>
     <row r="93" ht="32" customHeight="1">
       <c r="A93" s="2" t="n">
@@ -7924,11 +7800,11 @@
         <v/>
       </c>
       <c r="J93" s="2">
-        <f>IF(U93&lt;&gt;"",U93,INDEX(비용표!$A$13:$A$17,MATCH(I93,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I93,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K93" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J93,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I93,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -7958,7 +7834,6 @@
       <c r="R93" s="2" t="n"/>
       <c r="S93" s="2" t="n"/>
       <c r="T93" s="2" t="n"/>
-      <c r="U93" s="2" t="n"/>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -8002,11 +7877,11 @@
         <v/>
       </c>
       <c r="J94" s="2">
-        <f>IF(U94&lt;&gt;"",U94,INDEX(비용표!$A$13:$A$17,MATCH(I94,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I94,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K94" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J94,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I94,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -8040,7 +7915,6 @@
       <c r="R94" s="2" t="n"/>
       <c r="S94" s="2" t="n"/>
       <c r="T94" s="2" t="n"/>
-      <c r="U94" s="2" t="n"/>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="2" t="n">
@@ -8084,11 +7958,11 @@
         <v/>
       </c>
       <c r="J95" s="2">
-        <f>IF(U95&lt;&gt;"",U95,INDEX(비용표!$A$13:$A$17,MATCH(I95,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I95,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K95" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J95,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I95,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -8114,7 +7988,6 @@
           <t>grainRate</t>
         </is>
       </c>
-      <c r="U95" s="2" t="n"/>
     </row>
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -8158,11 +8031,11 @@
         <v/>
       </c>
       <c r="J96" s="2">
-        <f>IF(U96&lt;&gt;"",U96,INDEX(비용표!$A$13:$A$17,MATCH(I96,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I96,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K96" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J96,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I96,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -8188,7 +8061,6 @@
           <t>heal</t>
         </is>
       </c>
-      <c r="U96" s="2" t="n"/>
     </row>
     <row r="97" ht="32" customHeight="1">
       <c r="A97" s="2" t="n">
@@ -8232,11 +8104,11 @@
         <v/>
       </c>
       <c r="J97" s="2">
-        <f>IF(U97&lt;&gt;"",U97,INDEX(비용표!$A$13:$A$17,MATCH(I97,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I97,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K97" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J97,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I97,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -8266,7 +8138,6 @@
       <c r="R97" s="2" t="n"/>
       <c r="S97" s="2" t="n"/>
       <c r="T97" s="2" t="n"/>
-      <c r="U97" s="2" t="n"/>
     </row>
     <row r="98" ht="32" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -8310,11 +8181,11 @@
         <v/>
       </c>
       <c r="J98" s="2">
-        <f>IF(U98&lt;&gt;"",U98,INDEX(비용표!$A$13:$A$17,MATCH(I98,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I98,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K98" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J98,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I98,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -8348,7 +8219,6 @@
       <c r="R98" s="2" t="n"/>
       <c r="S98" s="2" t="n"/>
       <c r="T98" s="2" t="n"/>
-      <c r="U98" s="2" t="n"/>
     </row>
     <row r="99" ht="32" customHeight="1">
       <c r="A99" s="2" t="n">
@@ -8392,11 +8262,11 @@
         <v/>
       </c>
       <c r="J99" s="2">
-        <f>IF(U99&lt;&gt;"",U99,INDEX(비용표!$A$13:$A$17,MATCH(I99,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I99,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K99" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J99,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I99,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -8430,7 +8300,6 @@
         </is>
       </c>
       <c r="T99" s="2" t="n"/>
-      <c r="U99" s="2" t="n"/>
     </row>
     <row r="100" ht="32" customHeight="1">
       <c r="A100" s="2" t="n">
@@ -8474,11 +8343,11 @@
         <v/>
       </c>
       <c r="J100" s="2">
-        <f>IF(U100&lt;&gt;"",U100,INDEX(비용표!$A$13:$A$17,MATCH(I100,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I100,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K100" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J100,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I100,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -8508,7 +8377,6 @@
       <c r="R100" s="2" t="n"/>
       <c r="S100" s="2" t="n"/>
       <c r="T100" s="2" t="n"/>
-      <c r="U100" s="2" t="n"/>
     </row>
     <row r="101" ht="32" customHeight="1">
       <c r="A101" s="2" t="n">
@@ -8552,11 +8420,11 @@
         <v/>
       </c>
       <c r="J101" s="2">
-        <f>IF(U101&lt;&gt;"",U101,INDEX(비용표!$A$13:$A$17,MATCH(I101,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I101,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K101" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J101,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I101,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -8582,7 +8450,6 @@
           <t>grainRate</t>
         </is>
       </c>
-      <c r="U101" s="2" t="n"/>
     </row>
     <row r="102" ht="32" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -8626,11 +8493,11 @@
         <v/>
       </c>
       <c r="J102" s="2">
-        <f>IF(U102&lt;&gt;"",U102,INDEX(비용표!$A$13:$A$17,MATCH(I102,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I102,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K102" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J102,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I102,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -8660,7 +8527,6 @@
       <c r="R102" s="2" t="n"/>
       <c r="S102" s="2" t="n"/>
       <c r="T102" s="2" t="n"/>
-      <c r="U102" s="2" t="n"/>
     </row>
     <row r="103" ht="32" customHeight="1">
       <c r="A103" s="2" t="n">
@@ -8704,11 +8570,11 @@
         <v/>
       </c>
       <c r="J103" s="2">
-        <f>IF(U103&lt;&gt;"",U103,INDEX(비용표!$A$13:$A$17,MATCH(I103,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I103,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K103" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J103,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I103,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -8742,7 +8608,6 @@
         </is>
       </c>
       <c r="T103" s="2" t="n"/>
-      <c r="U103" s="2" t="n"/>
     </row>
     <row r="104" ht="32" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -8786,11 +8651,11 @@
         <v/>
       </c>
       <c r="J104" s="2">
-        <f>IF(U104&lt;&gt;"",U104,INDEX(비용표!$A$13:$A$17,MATCH(I104,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I104,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K104" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J104,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I104,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -8820,11 +8685,6 @@
       <c r="R104" s="2" t="n"/>
       <c r="S104" s="2" t="n"/>
       <c r="T104" s="2" t="n"/>
-      <c r="U104" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="105" ht="48" customHeight="1">
       <c r="A105" s="2" t="n">
@@ -8868,11 +8728,11 @@
         <v/>
       </c>
       <c r="J105" s="2">
-        <f>IF(U105&lt;&gt;"",U105,INDEX(비용표!$A$13:$A$17,MATCH(I105,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I105,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K105" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J105,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I105,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -8902,11 +8762,6 @@
         </is>
       </c>
       <c r="T105" s="2" t="n"/>
-      <c r="U105" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="106" ht="32" customHeight="1">
       <c r="A106" s="2" t="n">
@@ -8950,11 +8805,11 @@
         <v/>
       </c>
       <c r="J106" s="2">
-        <f>IF(U106&lt;&gt;"",U106,INDEX(비용표!$A$13:$A$17,MATCH(I106,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I106,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K106" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J106,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I106,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -8988,7 +8843,6 @@
       <c r="R106" s="2" t="n"/>
       <c r="S106" s="2" t="n"/>
       <c r="T106" s="2" t="n"/>
-      <c r="U106" s="2" t="n"/>
     </row>
     <row r="107" ht="32" customHeight="1">
       <c r="A107" s="2" t="n">
@@ -9032,11 +8886,11 @@
         <v/>
       </c>
       <c r="J107" s="2">
-        <f>IF(U107&lt;&gt;"",U107,INDEX(비용표!$A$13:$A$17,MATCH(I107,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I107,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K107" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J107,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I107,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -9066,7 +8920,6 @@
       <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
       <c r="T107" s="2" t="n"/>
-      <c r="U107" s="2" t="n"/>
     </row>
     <row r="108" ht="32" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -9110,11 +8963,11 @@
         <v/>
       </c>
       <c r="J108" s="2">
-        <f>IF(U108&lt;&gt;"",U108,INDEX(비용표!$A$13:$A$17,MATCH(I108,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I108,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K108" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J108,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I108,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -9148,7 +9001,6 @@
       <c r="R108" s="2" t="n"/>
       <c r="S108" s="2" t="n"/>
       <c r="T108" s="2" t="n"/>
-      <c r="U108" s="2" t="n"/>
     </row>
     <row r="109" ht="32" customHeight="1">
       <c r="A109" s="2" t="n">
@@ -9192,11 +9044,11 @@
         <v/>
       </c>
       <c r="J109" s="2">
-        <f>IF(U109&lt;&gt;"",U109,INDEX(비용표!$A$13:$A$17,MATCH(I109,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I109,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K109" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J109,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I109,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -9224,11 +9076,6 @@
       </c>
       <c r="S109" s="2" t="n"/>
       <c r="T109" s="2" t="n"/>
-      <c r="U109" s="2" t="inlineStr">
-        <is>
-          <t>천하</t>
-        </is>
-      </c>
     </row>
     <row r="110" ht="32" customHeight="1">
       <c r="A110" s="2" t="n">
@@ -9272,11 +9119,11 @@
         <v/>
       </c>
       <c r="J110" s="2">
-        <f>IF(U110&lt;&gt;"",U110,INDEX(비용표!$A$13:$A$17,MATCH(I110,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I110,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K110" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J110,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I110,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -9304,11 +9151,6 @@
       </c>
       <c r="S110" s="2" t="n"/>
       <c r="T110" s="2" t="n"/>
-      <c r="U110" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="111" ht="32" customHeight="1">
       <c r="A111" s="2" t="n">
@@ -9352,11 +9194,11 @@
         <v/>
       </c>
       <c r="J111" s="2">
-        <f>IF(U111&lt;&gt;"",U111,INDEX(비용표!$A$13:$A$17,MATCH(I111,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I111,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K111" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J111,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I111,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -9392,7 +9234,6 @@
       </c>
       <c r="S111" s="2" t="n"/>
       <c r="T111" s="2" t="n"/>
-      <c r="U111" s="2" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -9436,11 +9277,11 @@
         <v/>
       </c>
       <c r="J112" s="2">
-        <f>IF(U112&lt;&gt;"",U112,INDEX(비용표!$A$13:$A$17,MATCH(I112,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I112,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K112" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J112,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I112,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L112" s="4" t="inlineStr">
@@ -9476,7 +9317,6 @@
       </c>
       <c r="S112" s="2" t="n"/>
       <c r="T112" s="2" t="n"/>
-      <c r="U112" s="2" t="n"/>
     </row>
     <row r="113" ht="32" customHeight="1">
       <c r="A113" s="2" t="n">
@@ -9520,11 +9360,11 @@
         <v/>
       </c>
       <c r="J113" s="2">
-        <f>IF(U113&lt;&gt;"",U113,INDEX(비용표!$A$13:$A$17,MATCH(I113,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I113,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K113" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J113,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I113,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -9550,11 +9390,6 @@
           <t>raidLoot</t>
         </is>
       </c>
-      <c r="U113" s="2" t="inlineStr">
-        <is>
-          <t>전설</t>
-        </is>
-      </c>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="2" t="n">
@@ -9598,11 +9433,11 @@
         <v/>
       </c>
       <c r="J114" s="2">
-        <f>IF(U114&lt;&gt;"",U114,INDEX(비용표!$A$13:$A$17,MATCH(I114,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I114,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K114" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J114,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I114,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L114" s="4" t="inlineStr">
@@ -9636,7 +9471,6 @@
       <c r="R114" s="2" t="n"/>
       <c r="S114" s="2" t="n"/>
       <c r="T114" s="2" t="n"/>
-      <c r="U114" s="2" t="n"/>
     </row>
     <row r="115" ht="32" customHeight="1">
       <c r="A115" s="2" t="n">
@@ -9680,11 +9514,11 @@
         <v/>
       </c>
       <c r="J115" s="2">
-        <f>IF(U115&lt;&gt;"",U115,INDEX(비용표!$A$13:$A$17,MATCH(I115,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I115,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K115" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J115,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I115,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -9718,7 +9552,6 @@
       <c r="R115" s="2" t="n"/>
       <c r="S115" s="2" t="n"/>
       <c r="T115" s="2" t="n"/>
-      <c r="U115" s="2" t="n"/>
     </row>
     <row r="116" ht="32" customHeight="1">
       <c r="A116" s="2" t="n">
@@ -9762,11 +9595,11 @@
         <v/>
       </c>
       <c r="J116" s="2">
-        <f>IF(U116&lt;&gt;"",U116,INDEX(비용표!$A$13:$A$17,MATCH(I116,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I116,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K116" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J116,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I116,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L116" s="4" t="inlineStr">
@@ -9800,7 +9633,6 @@
       <c r="R116" s="2" t="n"/>
       <c r="S116" s="2" t="n"/>
       <c r="T116" s="2" t="n"/>
-      <c r="U116" s="2" t="n"/>
     </row>
     <row r="117" ht="32" customHeight="1">
       <c r="A117" s="2" t="n">
@@ -9844,11 +9676,11 @@
         <v/>
       </c>
       <c r="J117" s="2">
-        <f>IF(U117&lt;&gt;"",U117,INDEX(비용표!$A$13:$A$17,MATCH(I117,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I117,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K117" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J117,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I117,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -9878,7 +9710,6 @@
       <c r="R117" s="2" t="n"/>
       <c r="S117" s="2" t="n"/>
       <c r="T117" s="2" t="n"/>
-      <c r="U117" s="2" t="n"/>
     </row>
     <row r="118" ht="32" customHeight="1">
       <c r="A118" s="2" t="n">
@@ -9922,11 +9753,11 @@
         <v/>
       </c>
       <c r="J118" s="2">
-        <f>IF(U118&lt;&gt;"",U118,INDEX(비용표!$A$13:$A$17,MATCH(I118,비용표!$B$13:$B$17,1)))</f>
+        <f>INDEX(비용표!$A$13:$A$17,MATCH(I118,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="K118" s="2">
-        <f>INDEX(비용표!$C$13:$C$17,MATCH(J118,비용표!$A$13:$A$17,0))</f>
+        <f>INDEX(비용표!$C$13:$C$17,MATCH(I118,비용표!$B$13:$B$17,1))</f>
         <v/>
       </c>
       <c r="L118" s="4" t="inlineStr">
@@ -9952,10 +9783,9 @@
           <t>grainCap</t>
         </is>
       </c>
-      <c r="U118" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U118"/>
+  <autoFilter ref="A1:T118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -10236,7 +10066,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>300</v>
@@ -10254,18 +10084,22 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>S급 다섯 — 5칸 상한에서 비용의 천장 (2026-10-14)</t>
+        </is>
+      </c>
     </row>
     <row r="18"/>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>노란 칸(파란 글자)만 고치면 「칸」 · 「컬렉션」 시트의 비용 · 등급 · 점수가 다시 계산된다. 값은 2026-10-13 기획 세션 초안이다(3차: 카드는 컬렉션마다 장수당 1장).</t>
+          <t>노란 칸(파란 글자)만 고치면 「칸」 · 「컬렉션」 시트의 비용 · 등급 · 점수가 다시 계산된다. 값은 2026-10-13 기획 세션 초안이다(3차: 카드는 컬렉션마다 장수당 1장). 2026-10-14: 칸 5개 상한에 맞춰 전설 42 → 34, 천하 60 → 50.</t>
         </is>
       </c>
     </row>
@@ -26088,7 +25922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26287,18 +26121,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>등급 지정</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>등급은 비용 합으로 정하되, 「컬렉션」 시트의 「등급 지정」 칸을 채우면 그 등급을 따른다. 5칸 상한으로 칸을 줄인 23개가 원래 등급을 지키려고 쓴다 (2026-10-13).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/컬렉션.xlsx
+++ b/docs/컬렉션.xlsx
@@ -7,9 +7,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컬렉션" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비용표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="칸" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="한글 제목" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비용표" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="칸" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'컬렉션'!$A$1:$T$118</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -78,8 +79,11 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF7D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDD3BF"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -145,6 +154,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -9797,6 +9809,1797 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>타이틀</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>한글 제목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>도원결의</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>도원결의</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>황건적 토벌</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>황건적 토벌</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>온주참화웅</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>술이 식기 전에</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>호뢰관 삼영전여포</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>세 영웅, 여포와 싸우다</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>반동탁 연합군</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>열여덟 제후, 동탁을 치다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>장안 천도</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>불타는 낙양</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>칠성보도 헌상</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>조조, 동탁을 노리다</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>진궁의 결별</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>진궁, 조조를 떠나다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>형양의 추격</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>조홍, 말을 내주다</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>손견과 전국옥새</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>우물 속의 옥새</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>현산의 손견</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>강동의 호랑이 지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>백마의종</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>흰 말의 기병대</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>계교 전투</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>백마를 꺾은 쇠뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>이각과 곽사</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>서로를 물어뜯은 두 장수</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>헌제의 동귀</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>황제를 맞이하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>둔전제</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>땅을 일궈 군량을 쌓다</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>서주 양도</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>세 번 사양한 서주</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>술 취한 장비</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>술 취한 장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>원문사극</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>백오십 보의 화살</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>공융과 태사자</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>홀로 포위를 뚫다</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>인중여포 마중적토</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>사람 중엔 여포, 말 중엔 적토</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>함진영</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>깨지 못한 진은 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>하비성 백문루</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>여포, 백문루에 묶이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>진등 부자</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>두 얼굴의 부자</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>원술 칭제</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>꿀물 한 그릇</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>역경 함락</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>불타는 누대</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>신정산의 일기토</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>손책과 태사자, 맞붙다</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>내사는 장소에게</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>안은 장소에게, 밖은 주유에게</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>완성의 밤</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>아들과 명마를 잃은 밤</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>가후의 계책</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>쫓지 말라 할 때 쫓아라</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>청매자주 영웅론</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>천하의 영웅은 그대와 나뿐</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>의대조</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>옷 띠 속의 밀서</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>토산의 세 가지 약속</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>관우의 세 가지 약속</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>십승십패론</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>이길 이유 열 가지</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>왕좌지재</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>조조의 장자방</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>원소의 모사들</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>듣지 않는 주군</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>하북의 두 기둥</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>안량과 문추</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>관도대전</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>관도대전</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>오소 기습</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>군량고를 불태우다</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>오관참육장</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>다섯 관문, 여섯 장수</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>고성의 재회</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>형제, 다시 모이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>발시담정</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>화살을 뽑아 눈을 삼키다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>백랑산</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>북방 끝의 싸움</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>적로의 단계 도약</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>적로, 강을 뛰어넘다</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>팔문금쇄진</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>여덟 문의 진법</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>서서의 어머니</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>서서의 어머니</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>삼고초려</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>삼고초려</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>박망파의 불</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>제갈량의 첫 계책</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>형주의 항복</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>형주를 바치다</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>장판파 단기구주</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>백만 대군 속의 조운</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>장판교의 일갈</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>다리 위의 호통</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>상옥추제</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>사다리를 치우다</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>노숙의 합종</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>노숙, 동맹을 맺다</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>설전군유</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>말로 선비들을 꺾다</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>책상을 베다</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>책상을 베다</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>군영회</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>술자리의 가짜 편지</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>초선차전</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>풀배로 화살을 빌리다</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>고육지책</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>고육지책</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>방통의 연환계</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>쇠사슬로 묶은 배</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>칠성단의 동남풍</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>동남풍을 부르다</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>적벽대전</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>적벽대전</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>화용도</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>관우, 길을 열다</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>남군 공방</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>주유, 화살을 맞다</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>삼기주유</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>하늘은 어찌 나를 낳고…</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>장사의 노장</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>예순의 황충</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>감로사</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>진짜가 된 혼인</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>동작대부</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>조식의 노래</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>동관의 마초</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>수염을 자른 조조</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>서천 지도</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>지도 한 장</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>낙봉파</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>봉황이 떨어지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>의석 엄안</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>감동을 주고 충신을 얻다</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>가맹관 야전</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>횃불 아래의 승부</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>익주의 유장</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>난세에 어울리지 않던 주인</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>단도부회</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>칼 한 자루면 충분하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>유수구</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>아들을 낳으려면 손권처럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>빈 찬합</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>빈 찬합</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>백기겁위영</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>기병 백 명의 야습</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>합비 소요진</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>울음을 그치게 한 이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>괄목상대</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>괄목상대</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>정군산</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>절대 노인을 무시하지 마라</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>계륵</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>계륵</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>수엄칠군</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>일곱 군을 삼킨 물</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>관을 멘 방덕</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>관을 멘 방덕</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>백의도강</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>흰 옷을 입고 강을 건너다</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>맥성</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>관우가 붙잡히다</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>수선대</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>사백 년이 끝나다</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>칠보시</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>일곱 걸음의 시</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>아버지의 원수</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>아버지의 이름으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>오계의 만왕</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>감녕을 쓰러뜨린 화살</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>이릉대전</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>칠백 리를 태운 불</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>백제성 탁고</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>유비가 운명하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>서성의 가짜 성벽</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>서성의 가짜 성벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>칠종칠금</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>일곱 번 잡고 일곱 번 놓아주다</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>출사표</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>출사표</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>오두미도</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>쌀 다섯 말의 교단</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>천수의 강유</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>제갈량, 강유를 만나다</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>가정</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>산 위에 진을 치다</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>공성계</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>거문고를 타는 제갈량</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>진창 수성</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>스무 날을 버틴 성</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>목우유마</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>나무로 만든 소와 말</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>목문도</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>장합, 화살비에 쓰러지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>반골</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>누가 감히 나를 죽이랴</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>상방곡의 비</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>하늘이 내린 소나기</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>오장원</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>죽은 자가 산 자를 물리치다</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>고평릉</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>늙은 이리가 일어나다</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>구벌중원</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>아홉 번의 북벌</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>촉의 사상</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>제갈량 이후의 촉</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>오호대장군</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>오호대장군</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>오자양장</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>조조의 다섯 명장</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>동오 4대 도독</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>강동의 네 도독</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>위의 모사들</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>조조의 책사들</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>강동 호신</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>손씨 3대를 지킨 장수들</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>주태의 흉터</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>흉터마다 한 잔</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>하후 형제</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>하후 형제</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>마씨오상 백미최량</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>다섯 형제 중의 백미</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>서량의 마씨</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>서량을 달린 마씨 일가</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>형주의 유표</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>두 아들 사이에서</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
@@ -9987,7 +11790,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -10095,7 +11897,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
@@ -10108,7 +11909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25916,7 +27717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/컬렉션.xlsx
+++ b/docs/컬렉션.xlsx
@@ -8057,7 +8057,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>병원 치료 시간 −5%</t>
+          <t>병원 치료 시간 −50%</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="2" t="n"/>
       <c r="P96" s="2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="Q96" s="4" t="n"/>
       <c r="R96" s="2" t="n"/>

--- a/docs/컬렉션.xlsx
+++ b/docs/컬렉션.xlsx
@@ -820,7 +820,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>도적떼 약탈률 −1%p (도적 1명당 10% → 9%)</t>
+          <t>도적떼 약탈률 −10%p (30% → 20%)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="2" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>도적떼 약탈률 −2%p (도적 1명당 10% → 8%)</t>
+          <t>도적떼 약탈률 −10%p (30% → 20%)</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="2" t="n"/>
       <c r="P113" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q113" s="4" t="n"/>
       <c r="R113" s="2" t="n"/>

--- a/docs/컬렉션.xlsx
+++ b/docs/컬렉션.xlsx
@@ -32620,7 +32620,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>위속</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -32628,7 +32628,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G78" s="5">
@@ -34314,10 +34314,10 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>원소</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G123" s="5">
@@ -34352,10 +34352,10 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
@@ -34390,10 +34390,10 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>원소</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
@@ -34410,7 +34410,7 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G125" s="5">
@@ -34431,7 +34431,7 @@
         <v>38</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>안량</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -34448,7 +34448,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G126" s="5">
@@ -34469,7 +34469,7 @@
         <v>38</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>문추</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G127" s="5">
@@ -34504,10 +34504,10 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>원소</t>
+          <t>허유</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G128" s="5">
@@ -34542,10 +34542,10 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>안량</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -34562,7 +34562,7 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G129" s="5">
@@ -34580,10 +34580,10 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>문추</t>
+          <t>순우경</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -34600,7 +34600,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G130" s="5">
@@ -34621,7 +34621,7 @@
         <v>39</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>허유</t>
+          <t>원소</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G131" s="5">
@@ -34656,10 +34656,10 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -34694,10 +34694,10 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>순우경</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -34714,7 +34714,7 @@
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G133" s="5">
@@ -34732,10 +34732,10 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
@@ -34744,7 +34744,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>원소</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G134" s="5">
@@ -34773,25 +34773,23 @@
         <v>40</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>병기</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>청룡언월도</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
+      <c r="F135" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="G135" s="5">
         <f>IF(C135="카드",INDEX(비용표!$C$2:$C$7,MATCH(F135,비용표!$B$2:$B$7,0)),F135*INDEX(비용표!$C$8:$C$9,MATCH(C135,비용표!$B$8:$B$9,0)))</f>
@@ -34808,10 +34806,10 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
@@ -34820,7 +34818,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -34846,10 +34844,10 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
@@ -34858,7 +34856,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -34884,26 +34882,28 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>병기</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>청룡언월도</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F138" s="5" t="n">
-        <v>5</v>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="G138" s="5">
         <f>IF(C138="카드",INDEX(비용표!$C$2:$C$7,MATCH(F138,비용표!$B$2:$B$7,0)),F138*INDEX(비용표!$C$8:$C$9,MATCH(C138,비용표!$B$8:$B$9,0)))</f>
@@ -34923,7 +34923,7 @@
         <v>41</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>조운</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
@@ -34961,7 +34961,7 @@
         <v>41</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>주창</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -34978,7 +34978,7 @@
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G140" s="5">
@@ -34996,10 +34996,10 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>하후돈</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -35034,10 +35034,10 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>조운</t>
+          <t>조성</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -35054,7 +35054,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G142" s="5">
@@ -35072,10 +35072,10 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>주창</t>
+          <t>여포</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -35092,7 +35092,7 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G143" s="5">
@@ -35110,7 +35110,7 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B144" s="5" t="n">
         <v>1</v>
@@ -35122,7 +35122,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>하후돈</t>
+          <t>장료</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -35148,7 +35148,7 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B145" s="5" t="n">
         <v>2</v>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>조성</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
@@ -35168,7 +35168,7 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G145" s="5">
@@ -35186,7 +35186,7 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B146" s="5" t="n">
         <v>3</v>
@@ -35198,7 +35198,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>여포</t>
+          <t>곽가</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -35227,25 +35227,23 @@
         <v>43</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>장료</t>
+          <t>대완마</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
+      <c r="F147" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="G147" s="5">
         <f>IF(C147="카드",INDEX(비용표!$C$2:$C$7,MATCH(F147,비용표!$B$2:$B$7,0)),F147*INDEX(비용표!$C$8:$C$9,MATCH(C147,비용표!$B$8:$B$9,0)))</f>
@@ -35262,10 +35260,10 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
@@ -35274,7 +35272,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -35300,10 +35298,10 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
@@ -35312,7 +35310,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>곽가</t>
+          <t>채모</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -35320,7 +35318,7 @@
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G149" s="5">
@@ -35338,10 +35336,10 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
@@ -35350,14 +35348,14 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>대완마</t>
+          <t>적로</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G150" s="5">
         <f>IF(C150="카드",INDEX(비용표!$C$2:$C$7,MATCH(F150,비용표!$B$2:$B$7,0)),F150*INDEX(비용표!$C$8:$C$9,MATCH(C150,비용표!$B$8:$B$9,0)))</f>
@@ -35374,7 +35372,7 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B151" s="5" t="n">
         <v>1</v>
@@ -35386,7 +35384,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>서서</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
@@ -35412,7 +35410,7 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B152" s="5" t="n">
         <v>2</v>
@@ -35424,7 +35422,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>채모</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -35432,7 +35430,7 @@
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G152" s="5">
@@ -35450,26 +35448,28 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B153" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>적로</t>
+          <t>조인</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>3</v>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G153" s="5">
         <f>IF(C153="카드",INDEX(비용표!$C$2:$C$7,MATCH(F153,비용표!$B$2:$B$7,0)),F153*INDEX(비용표!$C$8:$C$9,MATCH(C153,비용표!$B$8:$B$9,0)))</f>
@@ -35486,7 +35486,7 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B154" s="5" t="n">
         <v>1</v>
@@ -35524,7 +35524,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B155" s="5" t="n">
         <v>2</v>
@@ -35536,7 +35536,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>정욱</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -35544,7 +35544,7 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G155" s="5">
@@ -35562,7 +35562,7 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B156" s="5" t="n">
         <v>3</v>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>조인</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G156" s="5">
@@ -35603,7 +35603,7 @@
         <v>46</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>서서</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
@@ -35641,7 +35641,7 @@
         <v>46</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>정욱</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
@@ -35658,7 +35658,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G158" s="5">
@@ -35676,10 +35676,10 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
@@ -35714,10 +35714,10 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
@@ -35752,10 +35752,10 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
@@ -35793,7 +35793,7 @@
         <v>47</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
@@ -35831,7 +35831,7 @@
         <v>47</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>서서</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
@@ -35866,10 +35866,10 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
@@ -35904,10 +35904,10 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>하후돈</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
@@ -35942,10 +35942,10 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>서서</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
@@ -35983,7 +35983,7 @@
         <v>48</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
@@ -36021,7 +36021,7 @@
         <v>48</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>하후돈</t>
+          <t>조운</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
@@ -36056,10 +36056,10 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>유종</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -36076,7 +36076,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G169" s="5">
@@ -36094,10 +36094,10 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>채모</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G170" s="5">
@@ -36132,10 +36132,10 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>조운</t>
+          <t>괴월</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
@@ -36152,7 +36152,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G171" s="5">
@@ -36173,7 +36173,7 @@
         <v>49</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>유종</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
@@ -36190,7 +36190,7 @@
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G172" s="5">
@@ -36211,7 +36211,7 @@
         <v>49</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>채모</t>
+          <t>유표</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
@@ -36246,10 +36246,10 @@
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>괴월</t>
+          <t>조운</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G174" s="5">
@@ -36284,10 +36284,10 @@
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>하후은</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
@@ -36304,7 +36304,7 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G175" s="5">
@@ -36322,10 +36322,10 @@
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>유표</t>
+          <t>유선</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
@@ -36342,7 +36342,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G176" s="5">
@@ -36363,7 +36363,7 @@
         <v>50</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>조운</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
@@ -36401,25 +36401,23 @@
         <v>50</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>병기</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>하후은</t>
+          <t>청강검</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="F178" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="G178" s="5">
         <f>IF(C178="카드",INDEX(비용표!$C$2:$C$7,MATCH(F178,비용표!$B$2:$B$7,0)),F178*INDEX(비용표!$C$8:$C$9,MATCH(C178,비용표!$B$8:$B$9,0)))</f>
@@ -36436,10 +36434,10 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
@@ -36448,7 +36446,7 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>유선</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
@@ -36456,7 +36454,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G179" s="5">
@@ -36474,10 +36472,10 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
@@ -36486,7 +36484,7 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>하후걸</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
@@ -36494,7 +36492,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G180" s="5">
@@ -36512,26 +36510,28 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>병기</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>청강검</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F181" s="5" t="n">
-        <v>4</v>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="G181" s="5">
         <f>IF(C181="카드",INDEX(비용표!$C$2:$C$7,MATCH(F181,비용표!$B$2:$B$7,0)),F181*INDEX(비용표!$C$8:$C$9,MATCH(C181,비용표!$B$8:$B$9,0)))</f>
@@ -36551,7 +36551,7 @@
         <v>51</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>장료</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
@@ -36589,25 +36589,23 @@
         <v>51</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>병기</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>하후걸</t>
+          <t>장팔사모</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="F183" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="G183" s="5">
         <f>IF(C183="카드",INDEX(비용표!$C$2:$C$7,MATCH(F183,비용표!$B$2:$B$7,0)),F183*INDEX(비용표!$C$8:$C$9,MATCH(C183,비용표!$B$8:$B$9,0)))</f>
@@ -36624,10 +36622,10 @@
     </row>
     <row r="184">
       <c r="A184" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
@@ -36636,7 +36634,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>유기</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
@@ -36644,7 +36642,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G184" s="5">
@@ -36662,10 +36660,10 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
@@ -36674,7 +36672,7 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>장료</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
@@ -36700,26 +36698,28 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>병기</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>장팔사모</t>
+          <t>유표</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F186" s="5" t="n">
-        <v>5</v>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G186" s="5">
         <f>IF(C186="카드",INDEX(비용표!$C$2:$C$7,MATCH(F186,비용표!$B$2:$B$7,0)),F186*INDEX(비용표!$C$8:$C$9,MATCH(C186,비용표!$B$8:$B$9,0)))</f>
@@ -36736,7 +36736,7 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B187" s="5" t="n">
         <v>1</v>
@@ -36748,7 +36748,7 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>유기</t>
+          <t>노숙</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
@@ -36756,7 +36756,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G187" s="5">
@@ -36774,7 +36774,7 @@
     </row>
     <row r="188">
       <c r="A188" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B188" s="5" t="n">
         <v>2</v>
@@ -36812,7 +36812,7 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B189" s="5" t="n">
         <v>3</v>
@@ -36824,7 +36824,7 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>유표</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
@@ -36832,7 +36832,7 @@
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G189" s="5">
@@ -36853,7 +36853,7 @@
         <v>53</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>노숙</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
@@ -36891,7 +36891,7 @@
         <v>53</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>유표</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
@@ -36908,7 +36908,7 @@
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G191" s="5">
@@ -36926,10 +36926,10 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
@@ -36964,10 +36964,10 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B193" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>장소</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
@@ -36984,7 +36984,7 @@
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G193" s="5">
@@ -37002,10 +37002,10 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B194" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>유표</t>
+          <t>우번</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
@@ -37043,7 +37043,7 @@
         <v>54</v>
       </c>
       <c r="B195" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>보즐</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G195" s="5">
@@ -37081,7 +37081,7 @@
         <v>54</v>
       </c>
       <c r="B196" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>장소</t>
+          <t>설종</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
@@ -37098,7 +37098,7 @@
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G196" s="5">
@@ -37116,10 +37116,10 @@
     </row>
     <row r="197">
       <c r="A197" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B197" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>우번</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
@@ -37136,7 +37136,7 @@
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G197" s="5">
@@ -37154,10 +37154,10 @@
     </row>
     <row r="198">
       <c r="A198" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B198" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>보즐</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
@@ -37174,7 +37174,7 @@
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G198" s="5">
@@ -37192,10 +37192,10 @@
     </row>
     <row r="199">
       <c r="A199" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B199" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>설종</t>
+          <t>노숙</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
@@ -37212,7 +37212,7 @@
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G199" s="5">
@@ -37230,7 +37230,7 @@
     </row>
     <row r="200">
       <c r="A200" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B200" s="5" t="n">
         <v>1</v>
@@ -37242,7 +37242,7 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
@@ -37268,7 +37268,7 @@
     </row>
     <row r="201">
       <c r="A201" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B201" s="5" t="n">
         <v>2</v>
@@ -37280,7 +37280,7 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>채모</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
@@ -37288,7 +37288,7 @@
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G201" s="5">
@@ -37309,7 +37309,7 @@
         <v>56</v>
       </c>
       <c r="B202" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>장윤</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
@@ -37326,7 +37326,7 @@
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G202" s="5">
@@ -37347,7 +37347,7 @@
         <v>56</v>
       </c>
       <c r="B203" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>채모</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
@@ -37364,7 +37364,7 @@
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G203" s="5">
@@ -37382,10 +37382,10 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B204" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>장윤</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
@@ -37402,7 +37402,7 @@
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G204" s="5">
@@ -37420,10 +37420,10 @@
     </row>
     <row r="205">
       <c r="A205" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B205" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">
@@ -37461,7 +37461,7 @@
         <v>57</v>
       </c>
       <c r="B206" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
@@ -37496,10 +37496,10 @@
     </row>
     <row r="207">
       <c r="A207" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B207" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
@@ -37534,10 +37534,10 @@
     </row>
     <row r="208">
       <c r="A208" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B208" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>황개</t>
         </is>
       </c>
       <c r="E208" s="5" t="n">
@@ -37554,7 +37554,7 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G208" s="5">
@@ -37575,7 +37575,7 @@
         <v>58</v>
       </c>
       <c r="B209" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>감택</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G209" s="5">
@@ -37613,7 +37613,7 @@
         <v>58</v>
       </c>
       <c r="B210" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>황개</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E210" s="5" t="n">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G210" s="5">
@@ -37648,10 +37648,10 @@
     </row>
     <row r="211">
       <c r="A211" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B211" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>감택</t>
+          <t>방통</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G211" s="5">
@@ -37686,10 +37686,10 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B212" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
     </row>
     <row r="213">
       <c r="A213" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B213" s="5" t="n">
         <v>1</v>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>방통</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
@@ -37762,7 +37762,7 @@
     </row>
     <row r="214">
       <c r="A214" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B214" s="5" t="n">
         <v>2</v>
@@ -37774,7 +37774,7 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>노숙</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
@@ -37803,7 +37803,7 @@
         <v>60</v>
       </c>
       <c r="B215" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
@@ -37841,7 +37841,7 @@
         <v>60</v>
       </c>
       <c r="B216" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>노숙</t>
+          <t>서성</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
@@ -37858,7 +37858,7 @@
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G216" s="5">
@@ -37879,25 +37879,23 @@
         <v>60</v>
       </c>
       <c r="B217" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>우선</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
+      <c r="F217" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="G217" s="5">
         <f>IF(C217="카드",INDEX(비용표!$C$2:$C$7,MATCH(F217,비용표!$B$2:$B$7,0)),F217*INDEX(비용표!$C$8:$C$9,MATCH(C217,비용표!$B$8:$B$9,0)))</f>
@@ -37914,10 +37912,10 @@
     </row>
     <row r="218">
       <c r="A218" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B218" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
@@ -37926,7 +37924,7 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>서성</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
@@ -37934,7 +37932,7 @@
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G218" s="5">
@@ -37952,26 +37950,28 @@
     </row>
     <row r="219">
       <c r="A219" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B219" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>우선</t>
+          <t>황개</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F219" s="5" t="n">
-        <v>4</v>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G219" s="5">
         <f>IF(C219="카드",INDEX(비용표!$C$2:$C$7,MATCH(F219,비용표!$B$2:$B$7,0)),F219*INDEX(비용표!$C$8:$C$9,MATCH(C219,비용표!$B$8:$B$9,0)))</f>
@@ -37991,7 +37991,7 @@
         <v>61</v>
       </c>
       <c r="B220" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E220" s="5" t="n">
@@ -38029,7 +38029,7 @@
         <v>61</v>
       </c>
       <c r="B221" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>황개</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G221" s="5">
@@ -38067,25 +38067,23 @@
         <v>61</v>
       </c>
       <c r="B222" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>아이템</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>폭약</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="C222" s="5" t="inlineStr">
-        <is>
-          <t>카드</t>
-        </is>
-      </c>
-      <c r="D222" s="5" t="inlineStr">
-        <is>
-          <t>제갈량</t>
-        </is>
-      </c>
-      <c r="E222" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F222" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
       </c>
       <c r="G222" s="5">
         <f>IF(C222="카드",INDEX(비용표!$C$2:$C$7,MATCH(F222,비용표!$B$2:$B$7,0)),F222*INDEX(비용표!$C$8:$C$9,MATCH(C222,비용표!$B$8:$B$9,0)))</f>
@@ -38102,10 +38100,10 @@
     </row>
     <row r="223">
       <c r="A223" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B223" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
@@ -38114,7 +38112,7 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E223" s="5" t="n">
@@ -38140,26 +38138,28 @@
     </row>
     <row r="224">
       <c r="A224" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B224" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>폭약</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F224" s="5" t="n">
-        <v>3</v>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="G224" s="5">
         <f>IF(C224="카드",INDEX(비용표!$C$2:$C$7,MATCH(F224,비용표!$B$2:$B$7,0)),F224*INDEX(비용표!$C$8:$C$9,MATCH(C224,비용표!$B$8:$B$9,0)))</f>
@@ -38176,7 +38176,7 @@
     </row>
     <row r="225">
       <c r="A225" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B225" s="5" t="n">
         <v>1</v>
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>조인</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
@@ -38196,7 +38196,7 @@
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G225" s="5">
@@ -38214,7 +38214,7 @@
     </row>
     <row r="226">
       <c r="A226" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B226" s="5" t="n">
         <v>2</v>
@@ -38226,7 +38226,7 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E226" s="5" t="n">
@@ -38252,7 +38252,7 @@
     </row>
     <row r="227">
       <c r="A227" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B227" s="5" t="n">
         <v>1</v>
@@ -38264,7 +38264,7 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>조인</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E227" s="5" t="n">
@@ -38272,7 +38272,7 @@
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G227" s="5">
@@ -38290,7 +38290,7 @@
     </row>
     <row r="228">
       <c r="A228" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B228" s="5" t="n">
         <v>2</v>
@@ -38302,7 +38302,7 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E228" s="5" t="n">
@@ -38328,7 +38328,7 @@
     </row>
     <row r="229">
       <c r="A229" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B229" s="5" t="n">
         <v>1</v>
@@ -38340,7 +38340,7 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>황충</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
@@ -38366,7 +38366,7 @@
     </row>
     <row r="230">
       <c r="A230" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B230" s="5" t="n">
         <v>2</v>
@@ -38378,7 +38378,7 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
@@ -38404,7 +38404,7 @@
     </row>
     <row r="231">
       <c r="A231" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B231" s="5" t="n">
         <v>1</v>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>황충</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E231" s="5" t="n">
@@ -38442,7 +38442,7 @@
     </row>
     <row r="232">
       <c r="A232" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B232" s="5" t="n">
         <v>2</v>
@@ -38454,7 +38454,7 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">
@@ -38483,7 +38483,7 @@
         <v>66</v>
       </c>
       <c r="B233" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E233" s="5" t="n">
@@ -38518,10 +38518,10 @@
     </row>
     <row r="234">
       <c r="A234" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B234" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>조식</t>
         </is>
       </c>
       <c r="E234" s="5" t="n">
@@ -38538,7 +38538,7 @@
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G234" s="5">
@@ -38556,10 +38556,10 @@
     </row>
     <row r="235">
       <c r="A235" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B235" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
@@ -38594,7 +38594,7 @@
     </row>
     <row r="236">
       <c r="A236" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B236" s="5" t="n">
         <v>1</v>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>조식</t>
+          <t>마초</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">
@@ -38614,7 +38614,7 @@
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G236" s="5">
@@ -38632,7 +38632,7 @@
     </row>
     <row r="237">
       <c r="A237" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B237" s="5" t="n">
         <v>2</v>
@@ -38644,7 +38644,7 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>마대</t>
         </is>
       </c>
       <c r="E237" s="5" t="n">
@@ -38652,7 +38652,7 @@
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G237" s="5">
@@ -38673,7 +38673,7 @@
         <v>68</v>
       </c>
       <c r="B238" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>마초</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E238" s="5" t="n">
@@ -38711,7 +38711,7 @@
         <v>68</v>
       </c>
       <c r="B239" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>마대</t>
+          <t>허저</t>
         </is>
       </c>
       <c r="E239" s="5" t="n">
@@ -38728,7 +38728,7 @@
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G239" s="5">
@@ -38749,7 +38749,7 @@
         <v>68</v>
       </c>
       <c r="B240" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>마등</t>
         </is>
       </c>
       <c r="E240" s="5" t="n">
@@ -38766,7 +38766,7 @@
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G240" s="5">
@@ -38784,10 +38784,10 @@
     </row>
     <row r="241">
       <c r="A241" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B241" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>허저</t>
+          <t>장송</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G241" s="5">
@@ -38822,10 +38822,10 @@
     </row>
     <row r="242">
       <c r="A242" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B242" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>마등</t>
+          <t>법정</t>
         </is>
       </c>
       <c r="E242" s="5" t="n">
@@ -38863,7 +38863,7 @@
         <v>69</v>
       </c>
       <c r="B243" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>장송</t>
+          <t>맹달</t>
         </is>
       </c>
       <c r="E243" s="5" t="n">
@@ -38880,7 +38880,7 @@
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G243" s="5">
@@ -38901,7 +38901,7 @@
         <v>69</v>
       </c>
       <c r="B244" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>법정</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E244" s="5" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G244" s="5">
@@ -38939,7 +38939,7 @@
         <v>69</v>
       </c>
       <c r="B245" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>맹달</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E245" s="5" t="n">
@@ -38956,7 +38956,7 @@
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G245" s="5">
@@ -38974,10 +38974,10 @@
     </row>
     <row r="246">
       <c r="A246" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B246" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>방통</t>
         </is>
       </c>
       <c r="E246" s="5" t="n">
@@ -39012,10 +39012,10 @@
     </row>
     <row r="247">
       <c r="A247" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B247" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>장임</t>
         </is>
       </c>
       <c r="E247" s="5" t="n">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G247" s="5">
@@ -39053,7 +39053,7 @@
         <v>70</v>
       </c>
       <c r="B248" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>방통</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E248" s="5" t="n">
@@ -39091,25 +39091,23 @@
         <v>70</v>
       </c>
       <c r="B249" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>장임</t>
+          <t>적로</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="F249" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="G249" s="5">
         <f>IF(C249="카드",INDEX(비용표!$C$2:$C$7,MATCH(F249,비용표!$B$2:$B$7,0)),F249*INDEX(비용표!$C$8:$C$9,MATCH(C249,비용표!$B$8:$B$9,0)))</f>
@@ -39126,10 +39124,10 @@
     </row>
     <row r="250">
       <c r="A250" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B250" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
@@ -39138,7 +39136,7 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>엄안</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">
@@ -39146,7 +39144,7 @@
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G250" s="5">
@@ -39164,26 +39162,28 @@
     </row>
     <row r="251">
       <c r="A251" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B251" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>적로</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F251" s="5" t="n">
-        <v>3</v>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="G251" s="5">
         <f>IF(C251="카드",INDEX(비용표!$C$2:$C$7,MATCH(F251,비용표!$B$2:$B$7,0)),F251*INDEX(비용표!$C$8:$C$9,MATCH(C251,비용표!$B$8:$B$9,0)))</f>
@@ -39200,7 +39200,7 @@
     </row>
     <row r="252">
       <c r="A252" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B252" s="5" t="n">
         <v>1</v>
@@ -39212,7 +39212,7 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>엄안</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
@@ -39220,7 +39220,7 @@
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G252" s="5">
@@ -39238,7 +39238,7 @@
     </row>
     <row r="253">
       <c r="A253" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B253" s="5" t="n">
         <v>2</v>
@@ -39250,7 +39250,7 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>마초</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">
@@ -39279,7 +39279,7 @@
         <v>72</v>
       </c>
       <c r="B254" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E254" s="5" t="n">
@@ -39314,10 +39314,10 @@
     </row>
     <row r="255">
       <c r="A255" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B255" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>마초</t>
+          <t>유장</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">
@@ -39334,7 +39334,7 @@
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G255" s="5">
@@ -39352,10 +39352,10 @@
     </row>
     <row r="256">
       <c r="A256" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B256" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>황권</t>
         </is>
       </c>
       <c r="E256" s="5" t="n">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G256" s="5">
@@ -39393,7 +39393,7 @@
         <v>73</v>
       </c>
       <c r="B257" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>유장</t>
+          <t>왕루</t>
         </is>
       </c>
       <c r="E257" s="5" t="n">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G257" s="5">
@@ -39431,7 +39431,7 @@
         <v>73</v>
       </c>
       <c r="B258" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>황권</t>
+          <t>장로</t>
         </is>
       </c>
       <c r="E258" s="5" t="n">
@@ -39448,7 +39448,7 @@
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G258" s="5">
@@ -39469,7 +39469,7 @@
         <v>73</v>
       </c>
       <c r="B259" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>왕루</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E259" s="5" t="n">
@@ -39486,7 +39486,7 @@
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G259" s="5">
@@ -39504,10 +39504,10 @@
     </row>
     <row r="260">
       <c r="A260" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B260" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>장로</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E260" s="5" t="n">
@@ -39524,7 +39524,7 @@
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G260" s="5">
@@ -39542,10 +39542,10 @@
     </row>
     <row r="261">
       <c r="A261" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B261" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>노숙</t>
         </is>
       </c>
       <c r="E261" s="5" t="n">
@@ -39583,7 +39583,7 @@
         <v>74</v>
       </c>
       <c r="B262" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>주창</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">
@@ -39600,7 +39600,7 @@
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G262" s="5">
@@ -39618,10 +39618,10 @@
     </row>
     <row r="263">
       <c r="A263" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B263" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>노숙</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E263" s="5" t="n">
@@ -39656,10 +39656,10 @@
     </row>
     <row r="264">
       <c r="A264" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B264" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>주창</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E264" s="5" t="n">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G264" s="5">
@@ -39697,7 +39697,7 @@
         <v>75</v>
       </c>
       <c r="B265" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>유종</t>
         </is>
       </c>
       <c r="E265" s="5" t="n">
@@ -39714,7 +39714,7 @@
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G265" s="5">
@@ -39732,10 +39732,10 @@
     </row>
     <row r="266">
       <c r="A266" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B266" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>순욱</t>
         </is>
       </c>
       <c r="E266" s="5" t="n">
@@ -39773,7 +39773,7 @@
         <v>76</v>
       </c>
       <c r="B267" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>순욱</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">
@@ -39808,10 +39808,10 @@
     </row>
     <row r="268">
       <c r="A268" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B268" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>감녕</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">
@@ -39849,7 +39849,7 @@
         <v>77</v>
       </c>
       <c r="B269" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>감녕</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">
@@ -39887,7 +39887,7 @@
         <v>77</v>
       </c>
       <c r="B270" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
@@ -39925,7 +39925,7 @@
         <v>77</v>
       </c>
       <c r="B271" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>장료</t>
         </is>
       </c>
       <c r="E271" s="5" t="n">
@@ -39960,10 +39960,10 @@
     </row>
     <row r="272">
       <c r="A272" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B272" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>78</v>
       </c>
       <c r="B273" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>장료</t>
+          <t>악진</t>
         </is>
       </c>
       <c r="E273" s="5" t="n">
@@ -40018,7 +40018,7 @@
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G273" s="5">
@@ -40039,7 +40039,7 @@
         <v>78</v>
       </c>
       <c r="B274" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>악진</t>
+          <t>이전</t>
         </is>
       </c>
       <c r="E274" s="5" t="n">
@@ -40056,7 +40056,7 @@
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G274" s="5">
@@ -40077,7 +40077,7 @@
         <v>78</v>
       </c>
       <c r="B275" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>이전</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E275" s="5" t="n">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G275" s="5">
@@ -40115,7 +40115,7 @@
         <v>78</v>
       </c>
       <c r="B276" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>감녕</t>
         </is>
       </c>
       <c r="E276" s="5" t="n">
@@ -40150,10 +40150,10 @@
     </row>
     <row r="277">
       <c r="A277" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B277" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>감녕</t>
+          <t>여몽</t>
         </is>
       </c>
       <c r="E277" s="5" t="n">
@@ -40191,7 +40191,7 @@
         <v>79</v>
       </c>
       <c r="B278" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>여몽</t>
+          <t>노숙</t>
         </is>
       </c>
       <c r="E278" s="5" t="n">
@@ -40229,7 +40229,7 @@
         <v>79</v>
       </c>
       <c r="B279" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>노숙</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E279" s="5" t="n">
@@ -40264,10 +40264,10 @@
     </row>
     <row r="280">
       <c r="A280" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B280" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>황충</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">
@@ -40305,7 +40305,7 @@
         <v>80</v>
       </c>
       <c r="B281" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>황충</t>
+          <t>하후연</t>
         </is>
       </c>
       <c r="E281" s="5" t="n">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G281" s="5">
@@ -40343,7 +40343,7 @@
         <v>80</v>
       </c>
       <c r="B282" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>하후연</t>
+          <t>법정</t>
         </is>
       </c>
       <c r="E282" s="5" t="n">
@@ -40381,25 +40381,23 @@
         <v>80</v>
       </c>
       <c r="B283" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>병기</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>법정</t>
+          <t>대감도</t>
         </is>
       </c>
       <c r="E283" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="F283" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="G283" s="5">
         <f>IF(C283="카드",INDEX(비용표!$C$2:$C$7,MATCH(F283,비용표!$B$2:$B$7,0)),F283*INDEX(비용표!$C$8:$C$9,MATCH(C283,비용표!$B$8:$B$9,0)))</f>
@@ -40419,23 +40417,23 @@
         <v>80</v>
       </c>
       <c r="B284" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>병기</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>대감도</t>
+          <t>영기</t>
         </is>
       </c>
       <c r="E284" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G284" s="5">
         <f>IF(C284="카드",INDEX(비용표!$C$2:$C$7,MATCH(F284,비용표!$B$2:$B$7,0)),F284*INDEX(비용표!$C$8:$C$9,MATCH(C284,비용표!$B$8:$B$9,0)))</f>
@@ -40452,26 +40450,28 @@
     </row>
     <row r="285">
       <c r="A285" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B285" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>영기</t>
+          <t>양수</t>
         </is>
       </c>
       <c r="E285" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F285" s="5" t="n">
-        <v>5</v>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G285" s="5">
         <f>IF(C285="카드",INDEX(비용표!$C$2:$C$7,MATCH(F285,비용표!$B$2:$B$7,0)),F285*INDEX(비용표!$C$8:$C$9,MATCH(C285,비용표!$B$8:$B$9,0)))</f>
@@ -40491,7 +40491,7 @@
         <v>81</v>
       </c>
       <c r="B286" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>양수</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G286" s="5">
@@ -40526,10 +40526,10 @@
     </row>
     <row r="287">
       <c r="A287" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B287" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E287" s="5" t="n">
@@ -40567,7 +40567,7 @@
         <v>82</v>
       </c>
       <c r="B288" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>우금</t>
         </is>
       </c>
       <c r="E288" s="5" t="n">
@@ -40584,7 +40584,7 @@
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G288" s="5">
@@ -40605,7 +40605,7 @@
         <v>82</v>
       </c>
       <c r="B289" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>우금</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E289" s="5" t="n">
@@ -40622,7 +40622,7 @@
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G289" s="5">
@@ -40640,10 +40640,10 @@
     </row>
     <row r="290">
       <c r="A290" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B290" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>방덕</t>
         </is>
       </c>
       <c r="E290" s="5" t="n">
@@ -40681,7 +40681,7 @@
         <v>83</v>
       </c>
       <c r="B291" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>방덕</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E291" s="5" t="n">
@@ -40716,10 +40716,10 @@
     </row>
     <row r="292">
       <c r="A292" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B292" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>여몽</t>
         </is>
       </c>
       <c r="E292" s="5" t="n">
@@ -40757,7 +40757,7 @@
         <v>84</v>
       </c>
       <c r="B293" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>여몽</t>
+          <t>육손</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
@@ -40795,7 +40795,7 @@
         <v>84</v>
       </c>
       <c r="B294" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>육손</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E294" s="5" t="n">
@@ -40833,7 +40833,7 @@
         <v>84</v>
       </c>
       <c r="B295" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>미방</t>
         </is>
       </c>
       <c r="E295" s="5" t="n">
@@ -40850,7 +40850,7 @@
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G295" s="5">
@@ -40871,7 +40871,7 @@
         <v>84</v>
       </c>
       <c r="B296" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>미방</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
@@ -40888,7 +40888,7 @@
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G296" s="5">
@@ -40906,10 +40906,10 @@
     </row>
     <row r="297">
       <c r="A297" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B297" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">
@@ -40947,7 +40947,7 @@
         <v>85</v>
       </c>
       <c r="B298" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>관평</t>
         </is>
       </c>
       <c r="E298" s="5" t="n">
@@ -40964,7 +40964,7 @@
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G298" s="5">
@@ -40985,7 +40985,7 @@
         <v>85</v>
       </c>
       <c r="B299" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>관평</t>
+          <t>주창</t>
         </is>
       </c>
       <c r="E299" s="5" t="n">
@@ -41023,7 +41023,7 @@
         <v>85</v>
       </c>
       <c r="B300" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>주창</t>
+          <t>요화</t>
         </is>
       </c>
       <c r="E300" s="5" t="n">
@@ -41040,7 +41040,7 @@
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G300" s="5">
@@ -41061,7 +41061,7 @@
         <v>85</v>
       </c>
       <c r="B301" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>요화</t>
+          <t>유봉</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">
@@ -41078,7 +41078,7 @@
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G301" s="5">
@@ -41096,10 +41096,10 @@
     </row>
     <row r="302">
       <c r="A302" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B302" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>유봉</t>
+          <t>조비</t>
         </is>
       </c>
       <c r="E302" s="5" t="n">
@@ -41137,7 +41137,7 @@
         <v>86</v>
       </c>
       <c r="B303" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>조비</t>
+          <t>헌제</t>
         </is>
       </c>
       <c r="E303" s="5" t="n">
@@ -41154,7 +41154,7 @@
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G303" s="5">
@@ -41175,7 +41175,7 @@
         <v>86</v>
       </c>
       <c r="B304" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>헌제</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E304" s="5" t="n">
@@ -41192,7 +41192,7 @@
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G304" s="5">
@@ -41210,10 +41210,10 @@
     </row>
     <row r="305">
       <c r="A305" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B305" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>조식</t>
         </is>
       </c>
       <c r="E305" s="5" t="n">
@@ -41230,7 +41230,7 @@
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G305" s="5">
@@ -41251,7 +41251,7 @@
         <v>87</v>
       </c>
       <c r="B306" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>조식</t>
+          <t>조비</t>
         </is>
       </c>
       <c r="E306" s="5" t="n">
@@ -41268,7 +41268,7 @@
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G306" s="5">
@@ -41286,10 +41286,10 @@
     </row>
     <row r="307">
       <c r="A307" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B307" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>조비</t>
+          <t>관흥</t>
         </is>
       </c>
       <c r="E307" s="5" t="n">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G307" s="5">
@@ -41327,7 +41327,7 @@
         <v>88</v>
       </c>
       <c r="B308" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>관흥</t>
+          <t>장포</t>
         </is>
       </c>
       <c r="E308" s="5" t="n">
@@ -41365,7 +41365,7 @@
         <v>88</v>
       </c>
       <c r="B309" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
@@ -41374,7 +41374,7 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>장포</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E309" s="5" t="n">
@@ -41382,7 +41382,7 @@
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G309" s="5">
@@ -41403,7 +41403,7 @@
         <v>88</v>
       </c>
       <c r="B310" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E310" s="5" t="n">
@@ -41441,7 +41441,7 @@
         <v>88</v>
       </c>
       <c r="B311" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E311" s="5" t="n">
@@ -41476,10 +41476,10 @@
     </row>
     <row r="312">
       <c r="A312" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B312" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>사마가</t>
         </is>
       </c>
       <c r="E312" s="5" t="n">
@@ -41496,7 +41496,7 @@
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G312" s="5">
@@ -41517,7 +41517,7 @@
         <v>89</v>
       </c>
       <c r="B313" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>사마가</t>
+          <t>감녕</t>
         </is>
       </c>
       <c r="E313" s="5" t="n">
@@ -41534,7 +41534,7 @@
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G313" s="5">
@@ -41555,7 +41555,7 @@
         <v>89</v>
       </c>
       <c r="B314" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>감녕</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E314" s="5" t="n">
@@ -41590,10 +41590,10 @@
     </row>
     <row r="315">
       <c r="A315" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B315" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>육손</t>
         </is>
       </c>
       <c r="E315" s="5" t="n">
@@ -41631,7 +41631,7 @@
         <v>90</v>
       </c>
       <c r="B316" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>육손</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E316" s="5" t="n">
@@ -41669,7 +41669,7 @@
         <v>90</v>
       </c>
       <c r="B317" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>주연</t>
         </is>
       </c>
       <c r="E317" s="5" t="n">
@@ -41686,7 +41686,7 @@
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G317" s="5">
@@ -41707,7 +41707,7 @@
         <v>90</v>
       </c>
       <c r="B318" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>주연</t>
+          <t>마량</t>
         </is>
       </c>
       <c r="E318" s="5" t="n">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G318" s="5">
@@ -41745,7 +41745,7 @@
         <v>90</v>
       </c>
       <c r="B319" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>마량</t>
+          <t>황권</t>
         </is>
       </c>
       <c r="E319" s="5" t="n">
@@ -41762,7 +41762,7 @@
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G319" s="5">
@@ -41780,10 +41780,10 @@
     </row>
     <row r="320">
       <c r="A320" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B320" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>황권</t>
+          <t>유비</t>
         </is>
       </c>
       <c r="E320" s="5" t="n">
@@ -41800,7 +41800,7 @@
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G320" s="5">
@@ -41821,7 +41821,7 @@
         <v>91</v>
       </c>
       <c r="B321" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>유비</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E321" s="5" t="n">
@@ -41859,7 +41859,7 @@
         <v>91</v>
       </c>
       <c r="B322" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>유선</t>
         </is>
       </c>
       <c r="E322" s="5" t="n">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G322" s="5">
@@ -41897,7 +41897,7 @@
         <v>91</v>
       </c>
       <c r="B323" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>유선</t>
+          <t>조비</t>
         </is>
       </c>
       <c r="E323" s="5" t="n">
@@ -41914,7 +41914,7 @@
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G323" s="5">
@@ -41932,10 +41932,10 @@
     </row>
     <row r="324">
       <c r="A324" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B324" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>조비</t>
+          <t>서성</t>
         </is>
       </c>
       <c r="E324" s="5" t="n">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G324" s="5">
@@ -41973,7 +41973,7 @@
         <v>92</v>
       </c>
       <c r="B325" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>서성</t>
+          <t>조비</t>
         </is>
       </c>
       <c r="E325" s="5" t="n">
@@ -41990,7 +41990,7 @@
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G325" s="5">
@@ -42008,10 +42008,10 @@
     </row>
     <row r="326">
       <c r="A326" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B326" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>조비</t>
+          <t>축융</t>
         </is>
       </c>
       <c r="E326" s="5" t="n">
@@ -42028,7 +42028,7 @@
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G326" s="5">
@@ -42049,7 +42049,7 @@
         <v>93</v>
       </c>
       <c r="B327" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>축융</t>
+          <t>오란</t>
         </is>
       </c>
       <c r="E327" s="5" t="n">
@@ -42066,7 +42066,7 @@
       </c>
       <c r="F327" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G327" s="5">
@@ -42087,7 +42087,7 @@
         <v>93</v>
       </c>
       <c r="B328" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>오란</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E328" s="5" t="n">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="F328" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G328" s="5">
@@ -42122,10 +42122,10 @@
     </row>
     <row r="329">
       <c r="A329" s="5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B329" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>94</v>
       </c>
       <c r="B330" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>유선</t>
         </is>
       </c>
       <c r="E330" s="5" t="n">
@@ -42180,7 +42180,7 @@
       </c>
       <c r="F330" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G330" s="5">
@@ -42198,10 +42198,10 @@
     </row>
     <row r="331">
       <c r="A331" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B331" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>유선</t>
+          <t>장로</t>
         </is>
       </c>
       <c r="E331" s="5" t="n">
@@ -42218,7 +42218,7 @@
       </c>
       <c r="F331" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G331" s="5">
@@ -42239,7 +42239,7 @@
         <v>95</v>
       </c>
       <c r="B332" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>장로</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E332" s="5" t="n">
@@ -42256,7 +42256,7 @@
       </c>
       <c r="F332" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G332" s="5">
@@ -42274,10 +42274,10 @@
     </row>
     <row r="333">
       <c r="A333" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B333" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>강유</t>
         </is>
       </c>
       <c r="E333" s="5" t="n">
@@ -42315,7 +42315,7 @@
         <v>96</v>
       </c>
       <c r="B334" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>강유</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E334" s="5" t="n">
@@ -42350,10 +42350,10 @@
     </row>
     <row r="335">
       <c r="A335" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B335" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>마속</t>
         </is>
       </c>
       <c r="E335" s="5" t="n">
@@ -42370,7 +42370,7 @@
       </c>
       <c r="F335" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G335" s="5">
@@ -42391,7 +42391,7 @@
         <v>97</v>
       </c>
       <c r="B336" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>마속</t>
+          <t>왕평</t>
         </is>
       </c>
       <c r="E336" s="5" t="n">
@@ -42429,7 +42429,7 @@
         <v>97</v>
       </c>
       <c r="B337" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>왕평</t>
+          <t>장합</t>
         </is>
       </c>
       <c r="E337" s="5" t="n">
@@ -42446,7 +42446,7 @@
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G337" s="5">
@@ -42467,7 +42467,7 @@
         <v>97</v>
       </c>
       <c r="B338" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>장합</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E338" s="5" t="n">
@@ -42502,10 +42502,10 @@
     </row>
     <row r="339">
       <c r="A339" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B339" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>98</v>
       </c>
       <c r="B340" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>사마의</t>
         </is>
       </c>
       <c r="E340" s="5" t="n">
@@ -42578,10 +42578,10 @@
     </row>
     <row r="341">
       <c r="A341" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B341" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>사마의</t>
+          <t>학소</t>
         </is>
       </c>
       <c r="E341" s="5" t="n">
@@ -42598,7 +42598,7 @@
       </c>
       <c r="F341" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G341" s="5">
@@ -42619,7 +42619,7 @@
         <v>99</v>
       </c>
       <c r="B342" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C342" s="5" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>학소</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E342" s="5" t="n">
@@ -42636,7 +42636,7 @@
       </c>
       <c r="F342" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G342" s="5">
@@ -42654,10 +42654,10 @@
     </row>
     <row r="343">
       <c r="A343" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B343" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>100</v>
       </c>
       <c r="B344" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>이엄</t>
         </is>
       </c>
       <c r="E344" s="5" t="n">
@@ -42712,7 +42712,7 @@
       </c>
       <c r="F344" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G344" s="5">
@@ -42733,25 +42733,23 @@
         <v>100</v>
       </c>
       <c r="B345" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>이엄</t>
+          <t>목우유마</t>
         </is>
       </c>
       <c r="E345" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F345" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="F345" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="G345" s="5">
         <f>IF(C345="카드",INDEX(비용표!$C$2:$C$7,MATCH(F345,비용표!$B$2:$B$7,0)),F345*INDEX(비용표!$C$8:$C$9,MATCH(C345,비용표!$B$8:$B$9,0)))</f>
@@ -42768,26 +42766,28 @@
     </row>
     <row r="346">
       <c r="A346" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B346" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>목우유마</t>
+          <t>장합</t>
         </is>
       </c>
       <c r="E346" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F346" s="5" t="n">
-        <v>4</v>
+      <c r="F346" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="G346" s="5">
         <f>IF(C346="카드",INDEX(비용표!$C$2:$C$7,MATCH(F346,비용표!$B$2:$B$7,0)),F346*INDEX(비용표!$C$8:$C$9,MATCH(C346,비용표!$B$8:$B$9,0)))</f>
@@ -42804,7 +42804,7 @@
     </row>
     <row r="347">
       <c r="A347" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B347" s="5" t="n">
         <v>1</v>
@@ -42816,7 +42816,7 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>장합</t>
+          <t>위연</t>
         </is>
       </c>
       <c r="E347" s="5" t="n">
@@ -42824,7 +42824,7 @@
       </c>
       <c r="F347" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G347" s="5">
@@ -42845,7 +42845,7 @@
         <v>102</v>
       </c>
       <c r="B348" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C348" s="5" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>위연</t>
+          <t>마대</t>
         </is>
       </c>
       <c r="E348" s="5" t="n">
@@ -42862,7 +42862,7 @@
       </c>
       <c r="F348" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G348" s="5">
@@ -42883,7 +42883,7 @@
         <v>102</v>
       </c>
       <c r="B349" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C349" s="5" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>마대</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E349" s="5" t="n">
@@ -42900,7 +42900,7 @@
       </c>
       <c r="F349" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G349" s="5">
@@ -42918,10 +42918,10 @@
     </row>
     <row r="350">
       <c r="A350" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B350" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C350" s="5" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>사마의</t>
         </is>
       </c>
       <c r="E350" s="5" t="n">
@@ -42959,7 +42959,7 @@
         <v>103</v>
       </c>
       <c r="B351" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C351" s="5" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>사마의</t>
+          <t>사마사</t>
         </is>
       </c>
       <c r="E351" s="5" t="n">
@@ -42976,7 +42976,7 @@
       </c>
       <c r="F351" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G351" s="5">
@@ -42997,7 +42997,7 @@
         <v>103</v>
       </c>
       <c r="B352" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C352" s="5" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>사마사</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E352" s="5" t="n">
@@ -43014,7 +43014,7 @@
       </c>
       <c r="F352" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G352" s="5">
@@ -43035,25 +43035,23 @@
         <v>103</v>
       </c>
       <c r="B353" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>아이템</t>
+        </is>
+      </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>폭약</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F353" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="C353" s="5" t="inlineStr">
-        <is>
-          <t>카드</t>
-        </is>
-      </c>
-      <c r="D353" s="5" t="inlineStr">
-        <is>
-          <t>제갈량</t>
-        </is>
-      </c>
-      <c r="E353" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F353" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
       </c>
       <c r="G353" s="5">
         <f>IF(C353="카드",INDEX(비용표!$C$2:$C$7,MATCH(F353,비용표!$B$2:$B$7,0)),F353*INDEX(비용표!$C$8:$C$9,MATCH(C353,비용표!$B$8:$B$9,0)))</f>
@@ -43070,26 +43068,28 @@
     </row>
     <row r="354">
       <c r="A354" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B354" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C354" s="5" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>카드</t>
         </is>
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>폭약</t>
+          <t>제갈량</t>
         </is>
       </c>
       <c r="E354" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F354" s="5" t="n">
-        <v>3</v>
+      <c r="F354" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="G354" s="5">
         <f>IF(C354="카드",INDEX(비용표!$C$2:$C$7,MATCH(F354,비용표!$B$2:$B$7,0)),F354*INDEX(비용표!$C$8:$C$9,MATCH(C354,비용표!$B$8:$B$9,0)))</f>
@@ -43109,7 +43109,7 @@
         <v>104</v>
       </c>
       <c r="B355" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C355" s="5" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>사마의</t>
         </is>
       </c>
       <c r="E355" s="5" t="n">
@@ -43147,7 +43147,7 @@
         <v>104</v>
       </c>
       <c r="B356" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C356" s="5" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>사마의</t>
+          <t>강유</t>
         </is>
       </c>
       <c r="E356" s="5" t="n">
@@ -43185,7 +43185,7 @@
         <v>104</v>
       </c>
       <c r="B357" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C357" s="5" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>강유</t>
+          <t>위연</t>
         </is>
       </c>
       <c r="E357" s="5" t="n">
@@ -43202,7 +43202,7 @@
       </c>
       <c r="F357" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G357" s="5">
@@ -43223,7 +43223,7 @@
         <v>104</v>
       </c>
       <c r="B358" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C358" s="5" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>위연</t>
+          <t>마대</t>
         </is>
       </c>
       <c r="E358" s="5" t="n">
@@ -43240,7 +43240,7 @@
       </c>
       <c r="F358" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G358" s="5">
@@ -43258,10 +43258,10 @@
     </row>
     <row r="359">
       <c r="A359" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B359" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C359" s="5" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>마대</t>
+          <t>사마의</t>
         </is>
       </c>
       <c r="E359" s="5" t="n">
@@ -43278,7 +43278,7 @@
       </c>
       <c r="F359" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G359" s="5">
@@ -43299,7 +43299,7 @@
         <v>105</v>
       </c>
       <c r="B360" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C360" s="5" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>사마의</t>
+          <t>사마사</t>
         </is>
       </c>
       <c r="E360" s="5" t="n">
@@ -43316,7 +43316,7 @@
       </c>
       <c r="F360" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G360" s="5">
@@ -43337,7 +43337,7 @@
         <v>105</v>
       </c>
       <c r="B361" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C361" s="5" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>사마사</t>
+          <t>사마소</t>
         </is>
       </c>
       <c r="E361" s="5" t="n">
@@ -43372,10 +43372,10 @@
     </row>
     <row r="362">
       <c r="A362" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B362" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>사마소</t>
+          <t>강유</t>
         </is>
       </c>
       <c r="E362" s="5" t="n">
@@ -43392,7 +43392,7 @@
       </c>
       <c r="F362" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G362" s="5">
@@ -43413,7 +43413,7 @@
         <v>106</v>
       </c>
       <c r="B363" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C363" s="5" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>강유</t>
+          <t>요화</t>
         </is>
       </c>
       <c r="E363" s="5" t="n">
@@ -43430,7 +43430,7 @@
       </c>
       <c r="F363" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G363" s="5">
@@ -43448,10 +43448,10 @@
     </row>
     <row r="364">
       <c r="A364" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B364" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>107</v>
       </c>
       <c r="B365" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C365" s="5" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>제갈량</t>
+          <t>장완</t>
         </is>
       </c>
       <c r="E365" s="5" t="n">
@@ -43506,7 +43506,7 @@
       </c>
       <c r="F365" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G365" s="5">
@@ -43527,7 +43527,7 @@
         <v>107</v>
       </c>
       <c r="B366" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C366" s="5" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>장완</t>
+          <t>비위</t>
         </is>
       </c>
       <c r="E366" s="5" t="n">
@@ -43544,7 +43544,7 @@
       </c>
       <c r="F366" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G366" s="5">
@@ -43562,10 +43562,10 @@
     </row>
     <row r="367">
       <c r="A367" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B367" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C367" s="5" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>비위</t>
+          <t>관우</t>
         </is>
       </c>
       <c r="E367" s="5" t="n">
@@ -43582,7 +43582,7 @@
       </c>
       <c r="F367" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G367" s="5">
@@ -43603,7 +43603,7 @@
         <v>108</v>
       </c>
       <c r="B368" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C368" s="5" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>관우</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="E368" s="5" t="n">
@@ -43641,7 +43641,7 @@
         <v>108</v>
       </c>
       <c r="B369" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C369" s="5" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>조운</t>
         </is>
       </c>
       <c r="E369" s="5" t="n">
@@ -43679,7 +43679,7 @@
         <v>108</v>
       </c>
       <c r="B370" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C370" s="5" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>조운</t>
+          <t>마초</t>
         </is>
       </c>
       <c r="E370" s="5" t="n">
@@ -43717,7 +43717,7 @@
         <v>108</v>
       </c>
       <c r="B371" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>마초</t>
+          <t>황충</t>
         </is>
       </c>
       <c r="E371" s="5" t="n">
@@ -43752,10 +43752,10 @@
     </row>
     <row r="372">
       <c r="A372" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B372" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C372" s="5" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>황충</t>
+          <t>장료</t>
         </is>
       </c>
       <c r="E372" s="5" t="n">
@@ -43793,7 +43793,7 @@
         <v>109</v>
       </c>
       <c r="B373" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C373" s="5" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>장료</t>
+          <t>악진</t>
         </is>
       </c>
       <c r="E373" s="5" t="n">
@@ -43810,7 +43810,7 @@
       </c>
       <c r="F373" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G373" s="5">
@@ -43831,7 +43831,7 @@
         <v>109</v>
       </c>
       <c r="B374" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C374" s="5" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>악진</t>
+          <t>우금</t>
         </is>
       </c>
       <c r="E374" s="5" t="n">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="F374" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G374" s="5">
@@ -43869,7 +43869,7 @@
         <v>109</v>
       </c>
       <c r="B375" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C375" s="5" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>우금</t>
+          <t>장합</t>
         </is>
       </c>
       <c r="E375" s="5" t="n">
@@ -43886,7 +43886,7 @@
       </c>
       <c r="F375" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G375" s="5">
@@ -43907,7 +43907,7 @@
         <v>109</v>
       </c>
       <c r="B376" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C376" s="5" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>장합</t>
+          <t>서황</t>
         </is>
       </c>
       <c r="E376" s="5" t="n">
@@ -43942,10 +43942,10 @@
     </row>
     <row r="377">
       <c r="A377" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B377" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C377" s="5" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>서황</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="E377" s="5" t="n">
@@ -43983,7 +43983,7 @@
         <v>110</v>
       </c>
       <c r="B378" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C378" s="5" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>주유</t>
+          <t>노숙</t>
         </is>
       </c>
       <c r="E378" s="5" t="n">
@@ -44021,7 +44021,7 @@
         <v>110</v>
       </c>
       <c r="B379" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C379" s="5" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>노숙</t>
+          <t>여몽</t>
         </is>
       </c>
       <c r="E379" s="5" t="n">
@@ -44059,7 +44059,7 @@
         <v>110</v>
       </c>
       <c r="B380" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C380" s="5" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>여몽</t>
+          <t>육손</t>
         </is>
       </c>
       <c r="E380" s="5" t="n">
@@ -44094,10 +44094,10 @@
     </row>
     <row r="381">
       <c r="A381" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B381" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C381" s="5" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>육손</t>
+          <t>순욱</t>
         </is>
       </c>
       <c r="E381" s="5" t="n">
@@ -44135,7 +44135,7 @@
         <v>111</v>
       </c>
       <c r="B382" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C382" s="5" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>순욱</t>
+          <t>순유</t>
         </is>
       </c>
       <c r="E382" s="5" t="n">
@@ -44152,7 +44152,7 @@
       </c>
       <c r="F382" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G382" s="5">
@@ -44173,7 +44173,7 @@
         <v>111</v>
       </c>
       <c r="B383" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C383" s="5" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>순유</t>
+          <t>곽가</t>
         </is>
       </c>
       <c r="E383" s="5" t="n">
@@ -44190,7 +44190,7 @@
       </c>
       <c r="F383" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G383" s="5">
@@ -44211,7 +44211,7 @@
         <v>111</v>
       </c>
       <c r="B384" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C384" s="5" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>곽가</t>
+          <t>가후</t>
         </is>
       </c>
       <c r="E384" s="5" t="n">
@@ -44249,7 +44249,7 @@
         <v>111</v>
       </c>
       <c r="B385" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C385" s="5" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>가후</t>
+          <t>사마의</t>
         </is>
       </c>
       <c r="E385" s="5" t="n">
@@ -44284,10 +44284,10 @@
     </row>
     <row r="386">
       <c r="A386" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B386" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C386" s="5" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>사마의</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="E386" s="5" t="n">
@@ -44304,7 +44304,7 @@
       </c>
       <c r="F386" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G386" s="5">
@@ -44325,7 +44325,7 @@
         <v>112</v>
       </c>
       <c r="B387" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C387" s="5" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>정보</t>
+          <t>황개</t>
         </is>
       </c>
       <c r="E387" s="5" t="n">
@@ -44363,7 +44363,7 @@
         <v>112</v>
       </c>
       <c r="B388" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C388" s="5" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>황개</t>
+          <t>주태</t>
         </is>
       </c>
       <c r="E388" s="5" t="n">
@@ -44401,7 +44401,7 @@
         <v>112</v>
       </c>
       <c r="B389" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C389" s="5" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>주태</t>
+          <t>감녕</t>
         </is>
       </c>
       <c r="E389" s="5" t="n">
@@ -44418,7 +44418,7 @@
       </c>
       <c r="F389" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G389" s="5">
@@ -44439,7 +44439,7 @@
         <v>112</v>
       </c>
       <c r="B390" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C390" s="5" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>감녕</t>
+          <t>능통</t>
         </is>
       </c>
       <c r="E390" s="5" t="n">
@@ -44456,7 +44456,7 @@
       </c>
       <c r="F390" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G390" s="5">
@@ -44474,10 +44474,10 @@
     </row>
     <row r="391">
       <c r="A391" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B391" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>능통</t>
+          <t>주태</t>
         </is>
       </c>
       <c r="E391" s="5" t="n">
@@ -44515,7 +44515,7 @@
         <v>113</v>
       </c>
       <c r="B392" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C392" s="5" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>주태</t>
+          <t>손권</t>
         </is>
       </c>
       <c r="E392" s="5" t="n">
@@ -44532,7 +44532,7 @@
       </c>
       <c r="F392" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G392" s="5">
@@ -44550,10 +44550,10 @@
     </row>
     <row r="393">
       <c r="A393" s="5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B393" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C393" s="5" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>손권</t>
+          <t>하후돈</t>
         </is>
       </c>
       <c r="E393" s="5" t="n">
@@ -44591,7 +44591,7 @@
         <v>114</v>
       </c>
       <c r="B394" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C394" s="5" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>하후돈</t>
+          <t>하후연</t>
         </is>
       </c>
       <c r="E394" s="5" t="n">
@@ -44608,7 +44608,7 @@
       </c>
       <c r="F394" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G394" s="5">
@@ -44629,7 +44629,7 @@
         <v>114</v>
       </c>
       <c r="B395" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C395" s="5" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>하후연</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E395" s="5" t="n">
@@ -44646,7 +44646,7 @@
       </c>
       <c r="F395" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G395" s="5">
@@ -44664,10 +44664,10 @@
     </row>
     <row r="396">
       <c r="A396" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B396" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C396" s="5" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>조조</t>
+          <t>마량</t>
         </is>
       </c>
       <c r="E396" s="5" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="F396" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G396" s="5">
@@ -44705,7 +44705,7 @@
         <v>115</v>
       </c>
       <c r="B397" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C397" s="5" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>마량</t>
+          <t>마속</t>
         </is>
       </c>
       <c r="E397" s="5" t="n">
@@ -44722,7 +44722,7 @@
       </c>
       <c r="F397" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G397" s="5">
@@ -44740,10 +44740,10 @@
     </row>
     <row r="398">
       <c r="A398" s="5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B398" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C398" s="5" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>마속</t>
+          <t>마등</t>
         </is>
       </c>
       <c r="E398" s="5" t="n">
@@ -44760,7 +44760,7 @@
       </c>
       <c r="F398" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G398" s="5">
@@ -44781,7 +44781,7 @@
         <v>116</v>
       </c>
       <c r="B399" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C399" s="5" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>마등</t>
+          <t>마초</t>
         </is>
       </c>
       <c r="E399" s="5" t="n">
@@ -44798,7 +44798,7 @@
       </c>
       <c r="F399" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G399" s="5">
@@ -44819,7 +44819,7 @@
         <v>116</v>
       </c>
       <c r="B400" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C400" s="5" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>마초</t>
+          <t>마대</t>
         </is>
       </c>
       <c r="E400" s="5" t="n">
@@ -44836,7 +44836,7 @@
       </c>
       <c r="F400" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G400" s="5">
@@ -44854,10 +44854,10 @@
     </row>
     <row r="401">
       <c r="A401" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B401" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C401" s="5" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>마대</t>
+          <t>유표</t>
         </is>
       </c>
       <c r="E401" s="5" t="n">
@@ -44895,7 +44895,7 @@
         <v>117</v>
       </c>
       <c r="B402" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C402" s="5" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>유표</t>
+          <t>유기</t>
         </is>
       </c>
       <c r="E402" s="5" t="n">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="F402" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G402" s="5">
@@ -44933,7 +44933,7 @@
         <v>117</v>
       </c>
       <c r="B403" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C403" s="5" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>유기</t>
+          <t>유종</t>
         </is>
       </c>
       <c r="E403" s="5" t="n">
@@ -44950,7 +44950,7 @@
       </c>
       <c r="F403" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G403" s="5">
@@ -44971,7 +44971,7 @@
         <v>117</v>
       </c>
       <c r="B404" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C404" s="5" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>유종</t>
+          <t>조조</t>
         </is>
       </c>
       <c r="E404" s="5" t="n">
@@ -44988,7 +44988,7 @@
       </c>
       <c r="F404" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G404" s="5">
@@ -45005,42 +45005,15 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="B405" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C405" s="5" t="inlineStr">
-        <is>
-          <t>카드</t>
-        </is>
-      </c>
-      <c r="D405" s="5" t="inlineStr">
-        <is>
-          <t>조조</t>
-        </is>
-      </c>
-      <c r="E405" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F405" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G405" s="5">
-        <f>IF(C405="카드",INDEX(비용표!$C$2:$C$7,MATCH(F405,비용표!$B$2:$B$7,0)),F405*INDEX(비용표!$C$8:$C$9,MATCH(C405,비용표!$B$8:$B$9,0)))</f>
-        <v/>
-      </c>
-      <c r="H405" s="5">
-        <f>G405*E405</f>
-        <v/>
-      </c>
-      <c r="I405" s="10">
-        <f>IF(A405=A404,I404&amp;" · ","")&amp;IF(C405="카드",D405&amp;E405,"["&amp;C405&amp;"] "&amp;D405)</f>
-        <v/>
-      </c>
+      <c r="A405" s="5" t="n"/>
+      <c r="B405" s="5" t="n"/>
+      <c r="C405" s="5" t="n"/>
+      <c r="D405" s="5" t="n"/>
+      <c r="E405" s="5" t="n"/>
+      <c r="F405" s="5" t="n"/>
+      <c r="G405" s="5" t="n"/>
+      <c r="H405" s="5" t="n"/>
+      <c r="I405" s="10" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
